--- a/packages/server/src/arpa_reporter/data/treasury/project215218BulkUpload.xlsx
+++ b/packages/server/src/arpa_reporter/data/treasury/project215218BulkUpload.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29622"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mac\Home\Documents\Projects\arpa-reporter\packages\server\src\arpa_reporter\data\treasury\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kgu82\Desktop\SLFRFBulkUploadTemplates\SLFRFBulkUploadTemplates\SLFRFBulkUploadTemplates\SLFRFBulkUploadTemplates\Quarter 4 2025 Project Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0666C880-DEF0-471E-902F-63688860EE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{C09C2177-8708-489A-8D0F-A85BC98D08C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{247CC77A-CACE-4412-9550-D28DA53D1845}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22875" windowHeight="13141" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1 " sheetId="2" r:id="rId1"/>
@@ -524,7 +524,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -595,12 +595,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -735,7 +741,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -976,7 +982,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{275FAA55-771D-4D64-A81A-E1231934DFE3}">
   <dimension ref="A1:AK1000"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="53" style="2" customWidth="1"/>
     <col min="2" max="5" width="35.625" style="2" customWidth="1"/>
@@ -993,7 +999,7 @@
     <col min="38" max="16384" width="12.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:37" ht="17.100000000000001" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1034,7 +1040,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:37" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
@@ -1075,7 +1081,7 @@
       <c r="AJ2" s="1"/>
       <c r="AK2" s="1"/>
     </row>
-    <row r="3" spans="1:37" ht="206.1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:37" ht="206.1" customHeight="1">
       <c r="A3" s="14" t="s">
         <v>2</v>
       </c>
@@ -1116,7 +1122,7 @@
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1"/>
     </row>
-    <row r="4" spans="1:37" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:37" ht="66.599999999999994" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1229,7 +1235,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:37" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:37" ht="13.15">
       <c r="A5" s="3" t="s">
         <v>40</v>
       </c>
@@ -1342,7 +1348,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="48.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:37" ht="48.95" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>44</v>
       </c>
@@ -1455,7 +1461,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:37" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:37" ht="409.6">
       <c r="A7" s="9" t="s">
         <v>80</v>
       </c>
@@ -1568,7 +1574,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:37" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:37" ht="42.75" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1607,7 +1613,7 @@
       <c r="AJ8" s="1"/>
       <c r="AK8" s="1"/>
     </row>
-    <row r="9" spans="1:37" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:37" ht="13.15">
       <c r="A9" s="15"/>
       <c r="B9" s="15"/>
       <c r="C9" s="1"/>
@@ -1646,7 +1652,7 @@
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
     </row>
-    <row r="10" spans="1:37" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:37" ht="13.15">
       <c r="A10" s="16"/>
       <c r="B10" s="16"/>
       <c r="C10" s="1"/>
@@ -1685,7 +1691,7 @@
       <c r="AJ10" s="1"/>
       <c r="AK10" s="1"/>
     </row>
-    <row r="11" spans="1:37" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:37" ht="13.15">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1724,7 +1730,7 @@
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
     </row>
-    <row r="12" spans="1:37" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:37" ht="13.15">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -1763,7 +1769,7 @@
       <c r="AJ12" s="1"/>
       <c r="AK12" s="1"/>
     </row>
-    <row r="13" spans="1:37" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:37" ht="13.15">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1802,7 +1808,7 @@
       <c r="AJ13" s="1"/>
       <c r="AK13" s="1"/>
     </row>
-    <row r="14" spans="1:37" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:37" ht="13.15">
       <c r="A14" s="6"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -1841,7 +1847,7 @@
       <c r="AJ14" s="1"/>
       <c r="AK14" s="1"/>
     </row>
-    <row r="15" spans="1:37" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:37" ht="13.15">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1880,7 +1886,7 @@
       <c r="AJ15" s="1"/>
       <c r="AK15" s="1"/>
     </row>
-    <row r="16" spans="1:37" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:37" ht="13.15">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1919,7 +1925,7 @@
       <c r="AJ16" s="1"/>
       <c r="AK16" s="1"/>
     </row>
-    <row r="17" spans="1:37" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:37" ht="13.15">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1958,7 +1964,7 @@
       <c r="AJ17" s="1"/>
       <c r="AK17" s="1"/>
     </row>
-    <row r="18" spans="1:37" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:37" ht="13.15">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1997,7 +2003,7 @@
       <c r="AJ18" s="1"/>
       <c r="AK18" s="1"/>
     </row>
-    <row r="19" spans="1:37" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:37" ht="13.15">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -2036,7 +2042,7 @@
       <c r="AJ19" s="1"/>
       <c r="AK19" s="1"/>
     </row>
-    <row r="20" spans="1:37" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:37" ht="13.15">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -2075,7 +2081,7 @@
       <c r="AJ20" s="1"/>
       <c r="AK20" s="1"/>
     </row>
-    <row r="21" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:37" ht="15.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -2114,7 +2120,7 @@
       <c r="AJ21" s="1"/>
       <c r="AK21" s="1"/>
     </row>
-    <row r="22" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:37" ht="15.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -2153,7 +2159,7 @@
       <c r="AJ22" s="1"/>
       <c r="AK22" s="1"/>
     </row>
-    <row r="23" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:37" ht="15.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -2192,7 +2198,7 @@
       <c r="AJ23" s="1"/>
       <c r="AK23" s="1"/>
     </row>
-    <row r="24" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:37" ht="15.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -2231,7 +2237,7 @@
       <c r="AJ24" s="1"/>
       <c r="AK24" s="1"/>
     </row>
-    <row r="25" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:37" ht="15.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -2270,7 +2276,7 @@
       <c r="AJ25" s="1"/>
       <c r="AK25" s="1"/>
     </row>
-    <row r="26" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:37" ht="15.95" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2309,7 +2315,7 @@
       <c r="AJ26" s="1"/>
       <c r="AK26" s="1"/>
     </row>
-    <row r="27" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:37" ht="15.95" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2348,7 +2354,7 @@
       <c r="AJ27" s="1"/>
       <c r="AK27" s="1"/>
     </row>
-    <row r="28" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:37" ht="15.95" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2387,7 +2393,7 @@
       <c r="AJ28" s="1"/>
       <c r="AK28" s="1"/>
     </row>
-    <row r="29" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:37" ht="15.95" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2426,7 +2432,7 @@
       <c r="AJ29" s="1"/>
       <c r="AK29" s="1"/>
     </row>
-    <row r="30" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:37" ht="15.95" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2465,7 +2471,7 @@
       <c r="AJ30" s="1"/>
       <c r="AK30" s="1"/>
     </row>
-    <row r="31" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:37" ht="15.95" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2504,7 +2510,7 @@
       <c r="AJ31" s="1"/>
       <c r="AK31" s="1"/>
     </row>
-    <row r="32" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:37" ht="15.95" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2543,7 +2549,7 @@
       <c r="AJ32" s="1"/>
       <c r="AK32" s="1"/>
     </row>
-    <row r="33" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:37" ht="15.95" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2582,7 +2588,7 @@
       <c r="AJ33" s="1"/>
       <c r="AK33" s="1"/>
     </row>
-    <row r="34" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:37" ht="15.95" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2621,7 +2627,7 @@
       <c r="AJ34" s="1"/>
       <c r="AK34" s="1"/>
     </row>
-    <row r="35" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:37" ht="15.95" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2660,7 +2666,7 @@
       <c r="AJ35" s="1"/>
       <c r="AK35" s="1"/>
     </row>
-    <row r="36" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:37" ht="15.95" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2699,7 +2705,7 @@
       <c r="AJ36" s="1"/>
       <c r="AK36" s="1"/>
     </row>
-    <row r="37" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:37" ht="15.95" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2738,7 +2744,7 @@
       <c r="AJ37" s="1"/>
       <c r="AK37" s="1"/>
     </row>
-    <row r="38" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:37" ht="15.95" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2777,7 +2783,7 @@
       <c r="AJ38" s="1"/>
       <c r="AK38" s="1"/>
     </row>
-    <row r="39" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:37" ht="15.95" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2816,7 +2822,7 @@
       <c r="AJ39" s="1"/>
       <c r="AK39" s="1"/>
     </row>
-    <row r="40" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:37" ht="15.95" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2855,7 +2861,7 @@
       <c r="AJ40" s="1"/>
       <c r="AK40" s="1"/>
     </row>
-    <row r="41" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:37" ht="15.95" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2894,7 +2900,7 @@
       <c r="AJ41" s="1"/>
       <c r="AK41" s="1"/>
     </row>
-    <row r="42" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:37" ht="15.95" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2933,7 +2939,7 @@
       <c r="AJ42" s="1"/>
       <c r="AK42" s="1"/>
     </row>
-    <row r="43" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:37" ht="15.95" customHeight="1">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2972,7 +2978,7 @@
       <c r="AJ43" s="1"/>
       <c r="AK43" s="1"/>
     </row>
-    <row r="44" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:37" ht="15.95" customHeight="1">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -3011,7 +3017,7 @@
       <c r="AJ44" s="1"/>
       <c r="AK44" s="1"/>
     </row>
-    <row r="45" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:37" ht="15.95" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -3050,7 +3056,7 @@
       <c r="AJ45" s="1"/>
       <c r="AK45" s="1"/>
     </row>
-    <row r="46" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:37" ht="15.95" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -3089,7 +3095,7 @@
       <c r="AJ46" s="1"/>
       <c r="AK46" s="1"/>
     </row>
-    <row r="47" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:37" ht="15.95" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -3128,7 +3134,7 @@
       <c r="AJ47" s="1"/>
       <c r="AK47" s="1"/>
     </row>
-    <row r="48" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:37" ht="15.95" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -3167,7 +3173,7 @@
       <c r="AJ48" s="1"/>
       <c r="AK48" s="1"/>
     </row>
-    <row r="49" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:37" ht="15.95" customHeight="1">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -3206,7 +3212,7 @@
       <c r="AJ49" s="1"/>
       <c r="AK49" s="1"/>
     </row>
-    <row r="50" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:37" ht="15.95" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -3245,7 +3251,7 @@
       <c r="AJ50" s="1"/>
       <c r="AK50" s="1"/>
     </row>
-    <row r="51" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:37" ht="15.95" customHeight="1">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -3284,7 +3290,7 @@
       <c r="AJ51" s="1"/>
       <c r="AK51" s="1"/>
     </row>
-    <row r="52" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:37" ht="15.95" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -3323,7 +3329,7 @@
       <c r="AJ52" s="1"/>
       <c r="AK52" s="1"/>
     </row>
-    <row r="53" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:37" ht="15.95" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -3362,7 +3368,7 @@
       <c r="AJ53" s="1"/>
       <c r="AK53" s="1"/>
     </row>
-    <row r="54" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:37" ht="15.95" customHeight="1">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -3401,7 +3407,7 @@
       <c r="AJ54" s="1"/>
       <c r="AK54" s="1"/>
     </row>
-    <row r="55" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:37" ht="15.95" customHeight="1">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -3440,7 +3446,7 @@
       <c r="AJ55" s="1"/>
       <c r="AK55" s="1"/>
     </row>
-    <row r="56" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:37" ht="15.95" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -3479,7 +3485,7 @@
       <c r="AJ56" s="1"/>
       <c r="AK56" s="1"/>
     </row>
-    <row r="57" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:37" ht="15.95" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -3518,7 +3524,7 @@
       <c r="AJ57" s="1"/>
       <c r="AK57" s="1"/>
     </row>
-    <row r="58" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:37" ht="15.95" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -3557,7 +3563,7 @@
       <c r="AJ58" s="1"/>
       <c r="AK58" s="1"/>
     </row>
-    <row r="59" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:37" ht="15.95" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -3596,7 +3602,7 @@
       <c r="AJ59" s="1"/>
       <c r="AK59" s="1"/>
     </row>
-    <row r="60" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:37" ht="15.95" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -3635,7 +3641,7 @@
       <c r="AJ60" s="1"/>
       <c r="AK60" s="1"/>
     </row>
-    <row r="61" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:37" ht="15.95" customHeight="1">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -3674,7 +3680,7 @@
       <c r="AJ61" s="1"/>
       <c r="AK61" s="1"/>
     </row>
-    <row r="62" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:37" ht="15.95" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -3713,7 +3719,7 @@
       <c r="AJ62" s="1"/>
       <c r="AK62" s="1"/>
     </row>
-    <row r="63" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:37" ht="15.95" customHeight="1">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -3752,7 +3758,7 @@
       <c r="AJ63" s="1"/>
       <c r="AK63" s="1"/>
     </row>
-    <row r="64" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:37" ht="15.95" customHeight="1">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -3791,7 +3797,7 @@
       <c r="AJ64" s="1"/>
       <c r="AK64" s="1"/>
     </row>
-    <row r="65" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:37" ht="15.95" customHeight="1">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -3830,7 +3836,7 @@
       <c r="AJ65" s="1"/>
       <c r="AK65" s="1"/>
     </row>
-    <row r="66" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:37" ht="15.95" customHeight="1">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -3869,7 +3875,7 @@
       <c r="AJ66" s="1"/>
       <c r="AK66" s="1"/>
     </row>
-    <row r="67" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:37" ht="15.95" customHeight="1">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -3908,7 +3914,7 @@
       <c r="AJ67" s="1"/>
       <c r="AK67" s="1"/>
     </row>
-    <row r="68" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:37" ht="15.95" customHeight="1">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3947,7 +3953,7 @@
       <c r="AJ68" s="1"/>
       <c r="AK68" s="1"/>
     </row>
-    <row r="69" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:37" ht="15.95" customHeight="1">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -3986,7 +3992,7 @@
       <c r="AJ69" s="1"/>
       <c r="AK69" s="1"/>
     </row>
-    <row r="70" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:37" ht="15.95" customHeight="1">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -4025,7 +4031,7 @@
       <c r="AJ70" s="1"/>
       <c r="AK70" s="1"/>
     </row>
-    <row r="71" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:37" ht="15.95" customHeight="1">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -4064,7 +4070,7 @@
       <c r="AJ71" s="1"/>
       <c r="AK71" s="1"/>
     </row>
-    <row r="72" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:37" ht="15.95" customHeight="1">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -4103,7 +4109,7 @@
       <c r="AJ72" s="1"/>
       <c r="AK72" s="1"/>
     </row>
-    <row r="73" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:37" ht="15.95" customHeight="1">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -4142,7 +4148,7 @@
       <c r="AJ73" s="1"/>
       <c r="AK73" s="1"/>
     </row>
-    <row r="74" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:37" ht="15.95" customHeight="1">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -4181,7 +4187,7 @@
       <c r="AJ74" s="1"/>
       <c r="AK74" s="1"/>
     </row>
-    <row r="75" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:37" ht="15.95" customHeight="1">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -4220,7 +4226,7 @@
       <c r="AJ75" s="1"/>
       <c r="AK75" s="1"/>
     </row>
-    <row r="76" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:37" ht="15.95" customHeight="1">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -4259,7 +4265,7 @@
       <c r="AJ76" s="1"/>
       <c r="AK76" s="1"/>
     </row>
-    <row r="77" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:37" ht="15.95" customHeight="1">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -4298,7 +4304,7 @@
       <c r="AJ77" s="1"/>
       <c r="AK77" s="1"/>
     </row>
-    <row r="78" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:37" ht="15.95" customHeight="1">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -4337,7 +4343,7 @@
       <c r="AJ78" s="1"/>
       <c r="AK78" s="1"/>
     </row>
-    <row r="79" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:37" ht="15.95" customHeight="1">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -4376,7 +4382,7 @@
       <c r="AJ79" s="1"/>
       <c r="AK79" s="1"/>
     </row>
-    <row r="80" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:37" ht="15.95" customHeight="1">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -4415,7 +4421,7 @@
       <c r="AJ80" s="1"/>
       <c r="AK80" s="1"/>
     </row>
-    <row r="81" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:37" ht="15.95" customHeight="1">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -4454,7 +4460,7 @@
       <c r="AJ81" s="1"/>
       <c r="AK81" s="1"/>
     </row>
-    <row r="82" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:37" ht="15.95" customHeight="1">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -4493,7 +4499,7 @@
       <c r="AJ82" s="1"/>
       <c r="AK82" s="1"/>
     </row>
-    <row r="83" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:37" ht="15.95" customHeight="1">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -4532,7 +4538,7 @@
       <c r="AJ83" s="1"/>
       <c r="AK83" s="1"/>
     </row>
-    <row r="84" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:37" ht="15.95" customHeight="1">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -4571,7 +4577,7 @@
       <c r="AJ84" s="1"/>
       <c r="AK84" s="1"/>
     </row>
-    <row r="85" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:37" ht="15.95" customHeight="1">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -4610,7 +4616,7 @@
       <c r="AJ85" s="1"/>
       <c r="AK85" s="1"/>
     </row>
-    <row r="86" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:37" ht="15.95" customHeight="1">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -4649,7 +4655,7 @@
       <c r="AJ86" s="1"/>
       <c r="AK86" s="1"/>
     </row>
-    <row r="87" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:37" ht="15.95" customHeight="1">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -4688,7 +4694,7 @@
       <c r="AJ87" s="1"/>
       <c r="AK87" s="1"/>
     </row>
-    <row r="88" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:37" ht="15.95" customHeight="1">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -4727,7 +4733,7 @@
       <c r="AJ88" s="1"/>
       <c r="AK88" s="1"/>
     </row>
-    <row r="89" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:37" ht="15.95" customHeight="1">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -4766,7 +4772,7 @@
       <c r="AJ89" s="1"/>
       <c r="AK89" s="1"/>
     </row>
-    <row r="90" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:37" ht="15.95" customHeight="1">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -4805,7 +4811,7 @@
       <c r="AJ90" s="1"/>
       <c r="AK90" s="1"/>
     </row>
-    <row r="91" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:37" ht="15.95" customHeight="1">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -4844,7 +4850,7 @@
       <c r="AJ91" s="1"/>
       <c r="AK91" s="1"/>
     </row>
-    <row r="92" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:37" ht="15.95" customHeight="1">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -4883,7 +4889,7 @@
       <c r="AJ92" s="1"/>
       <c r="AK92" s="1"/>
     </row>
-    <row r="93" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:37" ht="15.95" customHeight="1">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -4922,7 +4928,7 @@
       <c r="AJ93" s="1"/>
       <c r="AK93" s="1"/>
     </row>
-    <row r="94" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:37" ht="15.95" customHeight="1">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -4961,7 +4967,7 @@
       <c r="AJ94" s="1"/>
       <c r="AK94" s="1"/>
     </row>
-    <row r="95" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:37" ht="15.95" customHeight="1">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -5000,7 +5006,7 @@
       <c r="AJ95" s="1"/>
       <c r="AK95" s="1"/>
     </row>
-    <row r="96" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:37" ht="15.95" customHeight="1">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -5039,7 +5045,7 @@
       <c r="AJ96" s="1"/>
       <c r="AK96" s="1"/>
     </row>
-    <row r="97" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:37" ht="15.95" customHeight="1">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -5078,7 +5084,7 @@
       <c r="AJ97" s="1"/>
       <c r="AK97" s="1"/>
     </row>
-    <row r="98" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:37" ht="15.95" customHeight="1">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -5117,7 +5123,7 @@
       <c r="AJ98" s="1"/>
       <c r="AK98" s="1"/>
     </row>
-    <row r="99" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:37" ht="15.95" customHeight="1">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -5156,7 +5162,7 @@
       <c r="AJ99" s="1"/>
       <c r="AK99" s="1"/>
     </row>
-    <row r="100" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:37" ht="15.95" customHeight="1">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -5195,7 +5201,7 @@
       <c r="AJ100" s="1"/>
       <c r="AK100" s="1"/>
     </row>
-    <row r="101" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:37" ht="15.95" customHeight="1">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -5234,7 +5240,7 @@
       <c r="AJ101" s="1"/>
       <c r="AK101" s="1"/>
     </row>
-    <row r="102" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:37" ht="15.95" customHeight="1">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -5273,7 +5279,7 @@
       <c r="AJ102" s="1"/>
       <c r="AK102" s="1"/>
     </row>
-    <row r="103" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:37" ht="15.95" customHeight="1">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -5312,7 +5318,7 @@
       <c r="AJ103" s="1"/>
       <c r="AK103" s="1"/>
     </row>
-    <row r="104" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:37" ht="15.95" customHeight="1">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -5351,7 +5357,7 @@
       <c r="AJ104" s="1"/>
       <c r="AK104" s="1"/>
     </row>
-    <row r="105" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:37" ht="15.95" customHeight="1">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -5390,7 +5396,7 @@
       <c r="AJ105" s="1"/>
       <c r="AK105" s="1"/>
     </row>
-    <row r="106" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:37" ht="15.95" customHeight="1">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -5429,7 +5435,7 @@
       <c r="AJ106" s="1"/>
       <c r="AK106" s="1"/>
     </row>
-    <row r="107" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:37" ht="15.95" customHeight="1">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -5468,7 +5474,7 @@
       <c r="AJ107" s="1"/>
       <c r="AK107" s="1"/>
     </row>
-    <row r="108" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:37" ht="15.95" customHeight="1">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -5507,7 +5513,7 @@
       <c r="AJ108" s="1"/>
       <c r="AK108" s="1"/>
     </row>
-    <row r="109" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:37" ht="15.95" customHeight="1">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -5546,7 +5552,7 @@
       <c r="AJ109" s="1"/>
       <c r="AK109" s="1"/>
     </row>
-    <row r="110" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:37" ht="15.95" customHeight="1">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -5585,7 +5591,7 @@
       <c r="AJ110" s="1"/>
       <c r="AK110" s="1"/>
     </row>
-    <row r="111" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:37" ht="15.95" customHeight="1">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -5624,7 +5630,7 @@
       <c r="AJ111" s="1"/>
       <c r="AK111" s="1"/>
     </row>
-    <row r="112" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:37" ht="15.95" customHeight="1">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -5663,7 +5669,7 @@
       <c r="AJ112" s="1"/>
       <c r="AK112" s="1"/>
     </row>
-    <row r="113" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:37" ht="15.95" customHeight="1">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -5702,7 +5708,7 @@
       <c r="AJ113" s="1"/>
       <c r="AK113" s="1"/>
     </row>
-    <row r="114" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:37" ht="15.95" customHeight="1">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -5741,7 +5747,7 @@
       <c r="AJ114" s="1"/>
       <c r="AK114" s="1"/>
     </row>
-    <row r="115" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:37" ht="15.95" customHeight="1">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -5780,7 +5786,7 @@
       <c r="AJ115" s="1"/>
       <c r="AK115" s="1"/>
     </row>
-    <row r="116" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:37" ht="15.95" customHeight="1">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -5819,7 +5825,7 @@
       <c r="AJ116" s="1"/>
       <c r="AK116" s="1"/>
     </row>
-    <row r="117" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:37" ht="15.95" customHeight="1">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -5858,7 +5864,7 @@
       <c r="AJ117" s="1"/>
       <c r="AK117" s="1"/>
     </row>
-    <row r="118" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:37" ht="15.95" customHeight="1">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -5897,7 +5903,7 @@
       <c r="AJ118" s="1"/>
       <c r="AK118" s="1"/>
     </row>
-    <row r="119" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:37" ht="15.95" customHeight="1">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -5936,7 +5942,7 @@
       <c r="AJ119" s="1"/>
       <c r="AK119" s="1"/>
     </row>
-    <row r="120" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:37" ht="15.95" customHeight="1">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -5975,7 +5981,7 @@
       <c r="AJ120" s="1"/>
       <c r="AK120" s="1"/>
     </row>
-    <row r="121" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:37" ht="15.95" customHeight="1">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -6014,7 +6020,7 @@
       <c r="AJ121" s="1"/>
       <c r="AK121" s="1"/>
     </row>
-    <row r="122" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:37" ht="15.95" customHeight="1">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -6053,7 +6059,7 @@
       <c r="AJ122" s="1"/>
       <c r="AK122" s="1"/>
     </row>
-    <row r="123" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:37" ht="15.95" customHeight="1">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -6092,7 +6098,7 @@
       <c r="AJ123" s="1"/>
       <c r="AK123" s="1"/>
     </row>
-    <row r="124" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:37" ht="15.95" customHeight="1">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -6131,7 +6137,7 @@
       <c r="AJ124" s="1"/>
       <c r="AK124" s="1"/>
     </row>
-    <row r="125" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:37" ht="15.95" customHeight="1">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -6170,7 +6176,7 @@
       <c r="AJ125" s="1"/>
       <c r="AK125" s="1"/>
     </row>
-    <row r="126" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:37" ht="15.95" customHeight="1">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -6209,7 +6215,7 @@
       <c r="AJ126" s="1"/>
       <c r="AK126" s="1"/>
     </row>
-    <row r="127" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:37" ht="15.95" customHeight="1">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -6248,7 +6254,7 @@
       <c r="AJ127" s="1"/>
       <c r="AK127" s="1"/>
     </row>
-    <row r="128" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:37" ht="15.95" customHeight="1">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -6287,7 +6293,7 @@
       <c r="AJ128" s="1"/>
       <c r="AK128" s="1"/>
     </row>
-    <row r="129" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:37" ht="15.95" customHeight="1">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -6326,7 +6332,7 @@
       <c r="AJ129" s="1"/>
       <c r="AK129" s="1"/>
     </row>
-    <row r="130" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:37" ht="15.95" customHeight="1">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -6365,7 +6371,7 @@
       <c r="AJ130" s="1"/>
       <c r="AK130" s="1"/>
     </row>
-    <row r="131" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:37" ht="15.95" customHeight="1">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -6404,7 +6410,7 @@
       <c r="AJ131" s="1"/>
       <c r="AK131" s="1"/>
     </row>
-    <row r="132" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:37" ht="15.95" customHeight="1">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -6443,7 +6449,7 @@
       <c r="AJ132" s="1"/>
       <c r="AK132" s="1"/>
     </row>
-    <row r="133" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:37" ht="15.95" customHeight="1">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -6482,7 +6488,7 @@
       <c r="AJ133" s="1"/>
       <c r="AK133" s="1"/>
     </row>
-    <row r="134" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:37" ht="15.95" customHeight="1">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -6521,7 +6527,7 @@
       <c r="AJ134" s="1"/>
       <c r="AK134" s="1"/>
     </row>
-    <row r="135" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:37" ht="15.95" customHeight="1">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -6560,7 +6566,7 @@
       <c r="AJ135" s="1"/>
       <c r="AK135" s="1"/>
     </row>
-    <row r="136" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:37" ht="15.95" customHeight="1">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -6599,7 +6605,7 @@
       <c r="AJ136" s="1"/>
       <c r="AK136" s="1"/>
     </row>
-    <row r="137" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:37" ht="15.95" customHeight="1">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -6638,7 +6644,7 @@
       <c r="AJ137" s="1"/>
       <c r="AK137" s="1"/>
     </row>
-    <row r="138" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:37" ht="15.95" customHeight="1">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -6677,7 +6683,7 @@
       <c r="AJ138" s="1"/>
       <c r="AK138" s="1"/>
     </row>
-    <row r="139" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:37" ht="15.95" customHeight="1">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -6716,7 +6722,7 @@
       <c r="AJ139" s="1"/>
       <c r="AK139" s="1"/>
     </row>
-    <row r="140" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:37" ht="15.95" customHeight="1">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -6755,7 +6761,7 @@
       <c r="AJ140" s="1"/>
       <c r="AK140" s="1"/>
     </row>
-    <row r="141" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:37" ht="15.95" customHeight="1">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -6794,7 +6800,7 @@
       <c r="AJ141" s="1"/>
       <c r="AK141" s="1"/>
     </row>
-    <row r="142" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:37" ht="15.95" customHeight="1">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -6833,7 +6839,7 @@
       <c r="AJ142" s="1"/>
       <c r="AK142" s="1"/>
     </row>
-    <row r="143" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:37" ht="15.95" customHeight="1">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -6872,7 +6878,7 @@
       <c r="AJ143" s="1"/>
       <c r="AK143" s="1"/>
     </row>
-    <row r="144" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:37" ht="15.95" customHeight="1">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -6911,7 +6917,7 @@
       <c r="AJ144" s="1"/>
       <c r="AK144" s="1"/>
     </row>
-    <row r="145" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:37" ht="15.95" customHeight="1">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -6950,7 +6956,7 @@
       <c r="AJ145" s="1"/>
       <c r="AK145" s="1"/>
     </row>
-    <row r="146" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:37" ht="15.95" customHeight="1">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -6989,7 +6995,7 @@
       <c r="AJ146" s="1"/>
       <c r="AK146" s="1"/>
     </row>
-    <row r="147" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:37" ht="15.95" customHeight="1">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -7028,7 +7034,7 @@
       <c r="AJ147" s="1"/>
       <c r="AK147" s="1"/>
     </row>
-    <row r="148" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:37" ht="15.95" customHeight="1">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -7067,7 +7073,7 @@
       <c r="AJ148" s="1"/>
       <c r="AK148" s="1"/>
     </row>
-    <row r="149" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:37" ht="15.95" customHeight="1">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -7106,7 +7112,7 @@
       <c r="AJ149" s="1"/>
       <c r="AK149" s="1"/>
     </row>
-    <row r="150" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:37" ht="15.95" customHeight="1">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -7145,7 +7151,7 @@
       <c r="AJ150" s="1"/>
       <c r="AK150" s="1"/>
     </row>
-    <row r="151" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:37" ht="15.95" customHeight="1">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -7184,7 +7190,7 @@
       <c r="AJ151" s="1"/>
       <c r="AK151" s="1"/>
     </row>
-    <row r="152" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:37" ht="15.95" customHeight="1">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -7223,7 +7229,7 @@
       <c r="AJ152" s="1"/>
       <c r="AK152" s="1"/>
     </row>
-    <row r="153" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:37" ht="15.95" customHeight="1">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -7262,7 +7268,7 @@
       <c r="AJ153" s="1"/>
       <c r="AK153" s="1"/>
     </row>
-    <row r="154" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:37" ht="15.95" customHeight="1">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -7301,7 +7307,7 @@
       <c r="AJ154" s="1"/>
       <c r="AK154" s="1"/>
     </row>
-    <row r="155" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:37" ht="15.95" customHeight="1">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -7340,7 +7346,7 @@
       <c r="AJ155" s="1"/>
       <c r="AK155" s="1"/>
     </row>
-    <row r="156" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:37" ht="15.95" customHeight="1">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -7379,7 +7385,7 @@
       <c r="AJ156" s="1"/>
       <c r="AK156" s="1"/>
     </row>
-    <row r="157" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:37" ht="15.95" customHeight="1">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -7418,7 +7424,7 @@
       <c r="AJ157" s="1"/>
       <c r="AK157" s="1"/>
     </row>
-    <row r="158" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:37" ht="15.95" customHeight="1">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -7457,7 +7463,7 @@
       <c r="AJ158" s="1"/>
       <c r="AK158" s="1"/>
     </row>
-    <row r="159" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:37" ht="15.95" customHeight="1">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -7496,7 +7502,7 @@
       <c r="AJ159" s="1"/>
       <c r="AK159" s="1"/>
     </row>
-    <row r="160" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:37" ht="15.95" customHeight="1">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -7535,7 +7541,7 @@
       <c r="AJ160" s="1"/>
       <c r="AK160" s="1"/>
     </row>
-    <row r="161" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:37" ht="15.95" customHeight="1">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -7574,7 +7580,7 @@
       <c r="AJ161" s="1"/>
       <c r="AK161" s="1"/>
     </row>
-    <row r="162" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:37" ht="15.95" customHeight="1">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -7613,7 +7619,7 @@
       <c r="AJ162" s="1"/>
       <c r="AK162" s="1"/>
     </row>
-    <row r="163" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:37" ht="15.95" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -7652,7 +7658,7 @@
       <c r="AJ163" s="1"/>
       <c r="AK163" s="1"/>
     </row>
-    <row r="164" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:37" ht="15.95" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -7691,7 +7697,7 @@
       <c r="AJ164" s="1"/>
       <c r="AK164" s="1"/>
     </row>
-    <row r="165" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:37" ht="15.95" customHeight="1">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -7730,7 +7736,7 @@
       <c r="AJ165" s="1"/>
       <c r="AK165" s="1"/>
     </row>
-    <row r="166" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:37" ht="15.95" customHeight="1">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -7769,7 +7775,7 @@
       <c r="AJ166" s="1"/>
       <c r="AK166" s="1"/>
     </row>
-    <row r="167" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:37" ht="15.95" customHeight="1">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -7808,7 +7814,7 @@
       <c r="AJ167" s="1"/>
       <c r="AK167" s="1"/>
     </row>
-    <row r="168" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:37" ht="15.95" customHeight="1">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -7847,7 +7853,7 @@
       <c r="AJ168" s="1"/>
       <c r="AK168" s="1"/>
     </row>
-    <row r="169" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:37" ht="15.95" customHeight="1">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -7886,7 +7892,7 @@
       <c r="AJ169" s="1"/>
       <c r="AK169" s="1"/>
     </row>
-    <row r="170" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:37" ht="15.95" customHeight="1">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -7925,7 +7931,7 @@
       <c r="AJ170" s="1"/>
       <c r="AK170" s="1"/>
     </row>
-    <row r="171" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:37" ht="15.95" customHeight="1">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -7964,7 +7970,7 @@
       <c r="AJ171" s="1"/>
       <c r="AK171" s="1"/>
     </row>
-    <row r="172" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:37" ht="15.95" customHeight="1">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -8003,7 +8009,7 @@
       <c r="AJ172" s="1"/>
       <c r="AK172" s="1"/>
     </row>
-    <row r="173" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:37" ht="15.95" customHeight="1">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -8042,7 +8048,7 @@
       <c r="AJ173" s="1"/>
       <c r="AK173" s="1"/>
     </row>
-    <row r="174" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:37" ht="15.95" customHeight="1">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -8081,7 +8087,7 @@
       <c r="AJ174" s="1"/>
       <c r="AK174" s="1"/>
     </row>
-    <row r="175" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:37" ht="15.95" customHeight="1">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -8120,7 +8126,7 @@
       <c r="AJ175" s="1"/>
       <c r="AK175" s="1"/>
     </row>
-    <row r="176" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:37" ht="15.95" customHeight="1">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -8159,7 +8165,7 @@
       <c r="AJ176" s="1"/>
       <c r="AK176" s="1"/>
     </row>
-    <row r="177" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:37" ht="15.95" customHeight="1">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -8198,7 +8204,7 @@
       <c r="AJ177" s="1"/>
       <c r="AK177" s="1"/>
     </row>
-    <row r="178" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:37" ht="15.95" customHeight="1">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -8237,7 +8243,7 @@
       <c r="AJ178" s="1"/>
       <c r="AK178" s="1"/>
     </row>
-    <row r="179" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:37" ht="15.95" customHeight="1">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -8276,7 +8282,7 @@
       <c r="AJ179" s="1"/>
       <c r="AK179" s="1"/>
     </row>
-    <row r="180" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:37" ht="15.95" customHeight="1">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -8315,7 +8321,7 @@
       <c r="AJ180" s="1"/>
       <c r="AK180" s="1"/>
     </row>
-    <row r="181" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:37" ht="15.95" customHeight="1">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -8354,7 +8360,7 @@
       <c r="AJ181" s="1"/>
       <c r="AK181" s="1"/>
     </row>
-    <row r="182" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:37" ht="15.95" customHeight="1">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -8393,7 +8399,7 @@
       <c r="AJ182" s="1"/>
       <c r="AK182" s="1"/>
     </row>
-    <row r="183" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:37" ht="15.95" customHeight="1">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -8432,7 +8438,7 @@
       <c r="AJ183" s="1"/>
       <c r="AK183" s="1"/>
     </row>
-    <row r="184" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:37" ht="15.95" customHeight="1">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -8471,7 +8477,7 @@
       <c r="AJ184" s="1"/>
       <c r="AK184" s="1"/>
     </row>
-    <row r="185" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:37" ht="15.95" customHeight="1">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -8510,7 +8516,7 @@
       <c r="AJ185" s="1"/>
       <c r="AK185" s="1"/>
     </row>
-    <row r="186" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:37" ht="15.95" customHeight="1">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -8549,7 +8555,7 @@
       <c r="AJ186" s="1"/>
       <c r="AK186" s="1"/>
     </row>
-    <row r="187" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:37" ht="15.95" customHeight="1">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -8588,7 +8594,7 @@
       <c r="AJ187" s="1"/>
       <c r="AK187" s="1"/>
     </row>
-    <row r="188" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:37" ht="15.95" customHeight="1">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -8627,7 +8633,7 @@
       <c r="AJ188" s="1"/>
       <c r="AK188" s="1"/>
     </row>
-    <row r="189" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:37" ht="15.95" customHeight="1">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -8666,7 +8672,7 @@
       <c r="AJ189" s="1"/>
       <c r="AK189" s="1"/>
     </row>
-    <row r="190" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:37" ht="15.95" customHeight="1">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -8705,7 +8711,7 @@
       <c r="AJ190" s="1"/>
       <c r="AK190" s="1"/>
     </row>
-    <row r="191" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:37" ht="15.95" customHeight="1">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -8744,7 +8750,7 @@
       <c r="AJ191" s="1"/>
       <c r="AK191" s="1"/>
     </row>
-    <row r="192" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:37" ht="15.95" customHeight="1">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -8783,7 +8789,7 @@
       <c r="AJ192" s="1"/>
       <c r="AK192" s="1"/>
     </row>
-    <row r="193" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:37" ht="15.95" customHeight="1">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -8822,7 +8828,7 @@
       <c r="AJ193" s="1"/>
       <c r="AK193" s="1"/>
     </row>
-    <row r="194" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:37" ht="15.95" customHeight="1">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -8861,7 +8867,7 @@
       <c r="AJ194" s="1"/>
       <c r="AK194" s="1"/>
     </row>
-    <row r="195" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:37" ht="15.95" customHeight="1">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -8900,7 +8906,7 @@
       <c r="AJ195" s="1"/>
       <c r="AK195" s="1"/>
     </row>
-    <row r="196" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:37" ht="15.95" customHeight="1">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -8939,7 +8945,7 @@
       <c r="AJ196" s="1"/>
       <c r="AK196" s="1"/>
     </row>
-    <row r="197" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:37" ht="15.95" customHeight="1">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -8978,7 +8984,7 @@
       <c r="AJ197" s="1"/>
       <c r="AK197" s="1"/>
     </row>
-    <row r="198" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:37" ht="15.95" customHeight="1">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -9017,7 +9023,7 @@
       <c r="AJ198" s="1"/>
       <c r="AK198" s="1"/>
     </row>
-    <row r="199" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:37" ht="15.95" customHeight="1">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -9056,7 +9062,7 @@
       <c r="AJ199" s="1"/>
       <c r="AK199" s="1"/>
     </row>
-    <row r="200" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:37" ht="15.95" customHeight="1">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -9095,7 +9101,7 @@
       <c r="AJ200" s="1"/>
       <c r="AK200" s="1"/>
     </row>
-    <row r="201" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:37" ht="15.95" customHeight="1">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -9134,7 +9140,7 @@
       <c r="AJ201" s="1"/>
       <c r="AK201" s="1"/>
     </row>
-    <row r="202" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:37" ht="15.95" customHeight="1">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -9173,7 +9179,7 @@
       <c r="AJ202" s="1"/>
       <c r="AK202" s="1"/>
     </row>
-    <row r="203" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:37" ht="15.95" customHeight="1">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -9212,7 +9218,7 @@
       <c r="AJ203" s="1"/>
       <c r="AK203" s="1"/>
     </row>
-    <row r="204" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:37" ht="15.95" customHeight="1">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -9251,7 +9257,7 @@
       <c r="AJ204" s="1"/>
       <c r="AK204" s="1"/>
     </row>
-    <row r="205" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:37" ht="15.95" customHeight="1">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -9290,7 +9296,7 @@
       <c r="AJ205" s="1"/>
       <c r="AK205" s="1"/>
     </row>
-    <row r="206" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:37" ht="15.95" customHeight="1">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -9329,7 +9335,7 @@
       <c r="AJ206" s="1"/>
       <c r="AK206" s="1"/>
     </row>
-    <row r="207" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:37" ht="15.95" customHeight="1">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -9368,7 +9374,7 @@
       <c r="AJ207" s="1"/>
       <c r="AK207" s="1"/>
     </row>
-    <row r="208" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:37" ht="15.95" customHeight="1">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -9407,7 +9413,7 @@
       <c r="AJ208" s="1"/>
       <c r="AK208" s="1"/>
     </row>
-    <row r="209" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:37" ht="15.95" customHeight="1">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -9446,7 +9452,7 @@
       <c r="AJ209" s="1"/>
       <c r="AK209" s="1"/>
     </row>
-    <row r="210" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:37" ht="15.95" customHeight="1">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -9485,7 +9491,7 @@
       <c r="AJ210" s="1"/>
       <c r="AK210" s="1"/>
     </row>
-    <row r="211" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:37" ht="15.95" customHeight="1">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -9524,7 +9530,7 @@
       <c r="AJ211" s="1"/>
       <c r="AK211" s="1"/>
     </row>
-    <row r="212" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:37" ht="15.95" customHeight="1">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -9563,7 +9569,7 @@
       <c r="AJ212" s="1"/>
       <c r="AK212" s="1"/>
     </row>
-    <row r="213" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:37" ht="15.95" customHeight="1">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -9602,7 +9608,7 @@
       <c r="AJ213" s="1"/>
       <c r="AK213" s="1"/>
     </row>
-    <row r="214" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:37" ht="15.95" customHeight="1">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -9641,7 +9647,7 @@
       <c r="AJ214" s="1"/>
       <c r="AK214" s="1"/>
     </row>
-    <row r="215" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:37" ht="15.95" customHeight="1">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -9680,7 +9686,7 @@
       <c r="AJ215" s="1"/>
       <c r="AK215" s="1"/>
     </row>
-    <row r="216" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:37" ht="15.95" customHeight="1">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -9719,7 +9725,7 @@
       <c r="AJ216" s="1"/>
       <c r="AK216" s="1"/>
     </row>
-    <row r="217" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:37" ht="15.95" customHeight="1">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -9758,7 +9764,7 @@
       <c r="AJ217" s="1"/>
       <c r="AK217" s="1"/>
     </row>
-    <row r="218" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:37" ht="15.95" customHeight="1">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -9797,7 +9803,7 @@
       <c r="AJ218" s="1"/>
       <c r="AK218" s="1"/>
     </row>
-    <row r="219" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:37" ht="15.95" customHeight="1">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -9836,7 +9842,7 @@
       <c r="AJ219" s="1"/>
       <c r="AK219" s="1"/>
     </row>
-    <row r="220" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:37" ht="15.95" customHeight="1">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -9875,7 +9881,7 @@
       <c r="AJ220" s="1"/>
       <c r="AK220" s="1"/>
     </row>
-    <row r="221" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:37" ht="15.95" customHeight="1">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -9914,7 +9920,7 @@
       <c r="AJ221" s="1"/>
       <c r="AK221" s="1"/>
     </row>
-    <row r="222" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:37" ht="15.95" customHeight="1">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -9953,7 +9959,7 @@
       <c r="AJ222" s="1"/>
       <c r="AK222" s="1"/>
     </row>
-    <row r="223" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:37" ht="15.95" customHeight="1">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -9992,7 +9998,7 @@
       <c r="AJ223" s="1"/>
       <c r="AK223" s="1"/>
     </row>
-    <row r="224" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:37" ht="15.95" customHeight="1">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -10031,7 +10037,7 @@
       <c r="AJ224" s="1"/>
       <c r="AK224" s="1"/>
     </row>
-    <row r="225" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:37" ht="15.95" customHeight="1">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -10070,7 +10076,7 @@
       <c r="AJ225" s="1"/>
       <c r="AK225" s="1"/>
     </row>
-    <row r="226" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:37" ht="15.95" customHeight="1">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -10109,7 +10115,7 @@
       <c r="AJ226" s="1"/>
       <c r="AK226" s="1"/>
     </row>
-    <row r="227" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:37" ht="15.95" customHeight="1">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -10148,7 +10154,7 @@
       <c r="AJ227" s="1"/>
       <c r="AK227" s="1"/>
     </row>
-    <row r="228" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:37" ht="15.95" customHeight="1">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -10187,7 +10193,7 @@
       <c r="AJ228" s="1"/>
       <c r="AK228" s="1"/>
     </row>
-    <row r="229" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:37" ht="15.95" customHeight="1">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -10226,7 +10232,7 @@
       <c r="AJ229" s="1"/>
       <c r="AK229" s="1"/>
     </row>
-    <row r="230" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:37" ht="15.95" customHeight="1">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -10265,7 +10271,7 @@
       <c r="AJ230" s="1"/>
       <c r="AK230" s="1"/>
     </row>
-    <row r="231" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:37" ht="15.95" customHeight="1">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -10304,7 +10310,7 @@
       <c r="AJ231" s="1"/>
       <c r="AK231" s="1"/>
     </row>
-    <row r="232" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:37" ht="15.95" customHeight="1">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -10343,7 +10349,7 @@
       <c r="AJ232" s="1"/>
       <c r="AK232" s="1"/>
     </row>
-    <row r="233" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:37" ht="15.95" customHeight="1">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -10382,7 +10388,7 @@
       <c r="AJ233" s="1"/>
       <c r="AK233" s="1"/>
     </row>
-    <row r="234" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:37" ht="15.95" customHeight="1">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -10421,7 +10427,7 @@
       <c r="AJ234" s="1"/>
       <c r="AK234" s="1"/>
     </row>
-    <row r="235" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:37" ht="15.95" customHeight="1">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -10460,7 +10466,7 @@
       <c r="AJ235" s="1"/>
       <c r="AK235" s="1"/>
     </row>
-    <row r="236" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:37" ht="15.95" customHeight="1">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -10499,7 +10505,7 @@
       <c r="AJ236" s="1"/>
       <c r="AK236" s="1"/>
     </row>
-    <row r="237" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:37" ht="15.95" customHeight="1">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -10538,7 +10544,7 @@
       <c r="AJ237" s="1"/>
       <c r="AK237" s="1"/>
     </row>
-    <row r="238" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:37" ht="15.95" customHeight="1">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -10577,7 +10583,7 @@
       <c r="AJ238" s="1"/>
       <c r="AK238" s="1"/>
     </row>
-    <row r="239" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:37" ht="15.95" customHeight="1">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -10616,7 +10622,7 @@
       <c r="AJ239" s="1"/>
       <c r="AK239" s="1"/>
     </row>
-    <row r="240" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:37" ht="15.95" customHeight="1">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -10655,7 +10661,7 @@
       <c r="AJ240" s="1"/>
       <c r="AK240" s="1"/>
     </row>
-    <row r="241" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:37" ht="15.95" customHeight="1">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -10694,7 +10700,7 @@
       <c r="AJ241" s="1"/>
       <c r="AK241" s="1"/>
     </row>
-    <row r="242" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:37" ht="15.95" customHeight="1">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -10733,7 +10739,7 @@
       <c r="AJ242" s="1"/>
       <c r="AK242" s="1"/>
     </row>
-    <row r="243" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:37" ht="15.95" customHeight="1">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -10772,7 +10778,7 @@
       <c r="AJ243" s="1"/>
       <c r="AK243" s="1"/>
     </row>
-    <row r="244" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:37" ht="15.95" customHeight="1">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -10811,7 +10817,7 @@
       <c r="AJ244" s="1"/>
       <c r="AK244" s="1"/>
     </row>
-    <row r="245" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:37" ht="15.95" customHeight="1">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -10850,7 +10856,7 @@
       <c r="AJ245" s="1"/>
       <c r="AK245" s="1"/>
     </row>
-    <row r="246" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:37" ht="15.95" customHeight="1">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -10889,7 +10895,7 @@
       <c r="AJ246" s="1"/>
       <c r="AK246" s="1"/>
     </row>
-    <row r="247" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:37" ht="15.95" customHeight="1">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -10928,7 +10934,7 @@
       <c r="AJ247" s="1"/>
       <c r="AK247" s="1"/>
     </row>
-    <row r="248" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:37" ht="15.95" customHeight="1">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -10967,7 +10973,7 @@
       <c r="AJ248" s="1"/>
       <c r="AK248" s="1"/>
     </row>
-    <row r="249" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:37" ht="15.95" customHeight="1">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -11006,7 +11012,7 @@
       <c r="AJ249" s="1"/>
       <c r="AK249" s="1"/>
     </row>
-    <row r="250" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:37" ht="15.95" customHeight="1">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -11045,7 +11051,7 @@
       <c r="AJ250" s="1"/>
       <c r="AK250" s="1"/>
     </row>
-    <row r="251" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:37" ht="15.95" customHeight="1">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -11084,7 +11090,7 @@
       <c r="AJ251" s="1"/>
       <c r="AK251" s="1"/>
     </row>
-    <row r="252" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:37" ht="15.95" customHeight="1">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -11123,7 +11129,7 @@
       <c r="AJ252" s="1"/>
       <c r="AK252" s="1"/>
     </row>
-    <row r="253" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:37" ht="15.95" customHeight="1">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -11162,7 +11168,7 @@
       <c r="AJ253" s="1"/>
       <c r="AK253" s="1"/>
     </row>
-    <row r="254" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:37" ht="15.95" customHeight="1">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -11201,7 +11207,7 @@
       <c r="AJ254" s="1"/>
       <c r="AK254" s="1"/>
     </row>
-    <row r="255" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:37" ht="15.95" customHeight="1">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -11240,7 +11246,7 @@
       <c r="AJ255" s="1"/>
       <c r="AK255" s="1"/>
     </row>
-    <row r="256" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:37" ht="15.95" customHeight="1">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -11279,7 +11285,7 @@
       <c r="AJ256" s="1"/>
       <c r="AK256" s="1"/>
     </row>
-    <row r="257" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:37" ht="15.95" customHeight="1">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -11318,7 +11324,7 @@
       <c r="AJ257" s="1"/>
       <c r="AK257" s="1"/>
     </row>
-    <row r="258" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:37" ht="15.95" customHeight="1">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -11357,7 +11363,7 @@
       <c r="AJ258" s="1"/>
       <c r="AK258" s="1"/>
     </row>
-    <row r="259" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:37" ht="15.95" customHeight="1">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -11396,7 +11402,7 @@
       <c r="AJ259" s="1"/>
       <c r="AK259" s="1"/>
     </row>
-    <row r="260" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:37" ht="15.95" customHeight="1">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -11435,7 +11441,7 @@
       <c r="AJ260" s="1"/>
       <c r="AK260" s="1"/>
     </row>
-    <row r="261" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:37" ht="15.95" customHeight="1">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -11474,7 +11480,7 @@
       <c r="AJ261" s="1"/>
       <c r="AK261" s="1"/>
     </row>
-    <row r="262" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:37" ht="15.95" customHeight="1">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -11513,7 +11519,7 @@
       <c r="AJ262" s="1"/>
       <c r="AK262" s="1"/>
     </row>
-    <row r="263" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:37" ht="15.95" customHeight="1">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -11552,7 +11558,7 @@
       <c r="AJ263" s="1"/>
       <c r="AK263" s="1"/>
     </row>
-    <row r="264" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:37" ht="15.95" customHeight="1">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -11591,7 +11597,7 @@
       <c r="AJ264" s="1"/>
       <c r="AK264" s="1"/>
     </row>
-    <row r="265" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:37" ht="15.95" customHeight="1">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -11630,7 +11636,7 @@
       <c r="AJ265" s="1"/>
       <c r="AK265" s="1"/>
     </row>
-    <row r="266" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:37" ht="15.95" customHeight="1">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -11669,7 +11675,7 @@
       <c r="AJ266" s="1"/>
       <c r="AK266" s="1"/>
     </row>
-    <row r="267" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:37" ht="15.95" customHeight="1">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -11708,7 +11714,7 @@
       <c r="AJ267" s="1"/>
       <c r="AK267" s="1"/>
     </row>
-    <row r="268" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:37" ht="15.95" customHeight="1">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -11747,7 +11753,7 @@
       <c r="AJ268" s="1"/>
       <c r="AK268" s="1"/>
     </row>
-    <row r="269" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:37" ht="15.95" customHeight="1">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -11786,7 +11792,7 @@
       <c r="AJ269" s="1"/>
       <c r="AK269" s="1"/>
     </row>
-    <row r="270" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:37" ht="15.95" customHeight="1">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -11825,7 +11831,7 @@
       <c r="AJ270" s="1"/>
       <c r="AK270" s="1"/>
     </row>
-    <row r="271" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:37" ht="15.95" customHeight="1">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -11864,7 +11870,7 @@
       <c r="AJ271" s="1"/>
       <c r="AK271" s="1"/>
     </row>
-    <row r="272" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:37" ht="15.95" customHeight="1">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -11903,7 +11909,7 @@
       <c r="AJ272" s="1"/>
       <c r="AK272" s="1"/>
     </row>
-    <row r="273" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:37" ht="15.95" customHeight="1">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -11942,7 +11948,7 @@
       <c r="AJ273" s="1"/>
       <c r="AK273" s="1"/>
     </row>
-    <row r="274" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:37" ht="15.95" customHeight="1">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -11981,7 +11987,7 @@
       <c r="AJ274" s="1"/>
       <c r="AK274" s="1"/>
     </row>
-    <row r="275" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:37" ht="15.95" customHeight="1">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -12020,7 +12026,7 @@
       <c r="AJ275" s="1"/>
       <c r="AK275" s="1"/>
     </row>
-    <row r="276" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:37" ht="15.95" customHeight="1">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -12059,7 +12065,7 @@
       <c r="AJ276" s="1"/>
       <c r="AK276" s="1"/>
     </row>
-    <row r="277" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:37" ht="15.95" customHeight="1">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -12098,7 +12104,7 @@
       <c r="AJ277" s="1"/>
       <c r="AK277" s="1"/>
     </row>
-    <row r="278" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:37" ht="15.95" customHeight="1">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -12137,7 +12143,7 @@
       <c r="AJ278" s="1"/>
       <c r="AK278" s="1"/>
     </row>
-    <row r="279" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:37" ht="15.95" customHeight="1">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -12176,7 +12182,7 @@
       <c r="AJ279" s="1"/>
       <c r="AK279" s="1"/>
     </row>
-    <row r="280" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:37" ht="15.95" customHeight="1">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -12215,7 +12221,7 @@
       <c r="AJ280" s="1"/>
       <c r="AK280" s="1"/>
     </row>
-    <row r="281" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:37" ht="15.95" customHeight="1">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -12254,7 +12260,7 @@
       <c r="AJ281" s="1"/>
       <c r="AK281" s="1"/>
     </row>
-    <row r="282" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:37" ht="15.95" customHeight="1">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -12293,7 +12299,7 @@
       <c r="AJ282" s="1"/>
       <c r="AK282" s="1"/>
     </row>
-    <row r="283" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:37" ht="15.95" customHeight="1">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -12332,7 +12338,7 @@
       <c r="AJ283" s="1"/>
       <c r="AK283" s="1"/>
     </row>
-    <row r="284" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:37" ht="15.95" customHeight="1">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -12371,7 +12377,7 @@
       <c r="AJ284" s="1"/>
       <c r="AK284" s="1"/>
     </row>
-    <row r="285" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:37" ht="15.95" customHeight="1">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -12410,7 +12416,7 @@
       <c r="AJ285" s="1"/>
       <c r="AK285" s="1"/>
     </row>
-    <row r="286" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:37" ht="15.95" customHeight="1">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -12449,7 +12455,7 @@
       <c r="AJ286" s="1"/>
       <c r="AK286" s="1"/>
     </row>
-    <row r="287" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:37" ht="15.95" customHeight="1">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -12488,7 +12494,7 @@
       <c r="AJ287" s="1"/>
       <c r="AK287" s="1"/>
     </row>
-    <row r="288" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:37" ht="15.95" customHeight="1">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -12527,7 +12533,7 @@
       <c r="AJ288" s="1"/>
       <c r="AK288" s="1"/>
     </row>
-    <row r="289" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:37" ht="15.95" customHeight="1">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -12566,7 +12572,7 @@
       <c r="AJ289" s="1"/>
       <c r="AK289" s="1"/>
     </row>
-    <row r="290" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:37" ht="15.95" customHeight="1">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -12605,7 +12611,7 @@
       <c r="AJ290" s="1"/>
       <c r="AK290" s="1"/>
     </row>
-    <row r="291" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:37" ht="15.95" customHeight="1">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -12644,7 +12650,7 @@
       <c r="AJ291" s="1"/>
       <c r="AK291" s="1"/>
     </row>
-    <row r="292" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:37" ht="15.95" customHeight="1">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -12683,7 +12689,7 @@
       <c r="AJ292" s="1"/>
       <c r="AK292" s="1"/>
     </row>
-    <row r="293" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:37" ht="15.95" customHeight="1">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -12722,7 +12728,7 @@
       <c r="AJ293" s="1"/>
       <c r="AK293" s="1"/>
     </row>
-    <row r="294" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:37" ht="15.95" customHeight="1">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -12761,7 +12767,7 @@
       <c r="AJ294" s="1"/>
       <c r="AK294" s="1"/>
     </row>
-    <row r="295" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:37" ht="15.95" customHeight="1">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -12800,7 +12806,7 @@
       <c r="AJ295" s="1"/>
       <c r="AK295" s="1"/>
     </row>
-    <row r="296" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:37" ht="15.95" customHeight="1">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -12839,7 +12845,7 @@
       <c r="AJ296" s="1"/>
       <c r="AK296" s="1"/>
     </row>
-    <row r="297" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:37" ht="15.95" customHeight="1">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -12878,7 +12884,7 @@
       <c r="AJ297" s="1"/>
       <c r="AK297" s="1"/>
     </row>
-    <row r="298" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:37" ht="15.95" customHeight="1">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -12917,7 +12923,7 @@
       <c r="AJ298" s="1"/>
       <c r="AK298" s="1"/>
     </row>
-    <row r="299" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:37" ht="15.95" customHeight="1">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -12956,7 +12962,7 @@
       <c r="AJ299" s="1"/>
       <c r="AK299" s="1"/>
     </row>
-    <row r="300" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:37" ht="15.95" customHeight="1">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -12995,7 +13001,7 @@
       <c r="AJ300" s="1"/>
       <c r="AK300" s="1"/>
     </row>
-    <row r="301" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:37" ht="15.95" customHeight="1">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -13034,7 +13040,7 @@
       <c r="AJ301" s="1"/>
       <c r="AK301" s="1"/>
     </row>
-    <row r="302" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:37" ht="15.95" customHeight="1">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -13073,7 +13079,7 @@
       <c r="AJ302" s="1"/>
       <c r="AK302" s="1"/>
     </row>
-    <row r="303" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:37" ht="15.95" customHeight="1">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -13112,7 +13118,7 @@
       <c r="AJ303" s="1"/>
       <c r="AK303" s="1"/>
     </row>
-    <row r="304" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:37" ht="15.95" customHeight="1">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -13151,7 +13157,7 @@
       <c r="AJ304" s="1"/>
       <c r="AK304" s="1"/>
     </row>
-    <row r="305" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:37" ht="15.95" customHeight="1">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -13190,7 +13196,7 @@
       <c r="AJ305" s="1"/>
       <c r="AK305" s="1"/>
     </row>
-    <row r="306" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:37" ht="15.95" customHeight="1">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -13229,7 +13235,7 @@
       <c r="AJ306" s="1"/>
       <c r="AK306" s="1"/>
     </row>
-    <row r="307" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:37" ht="15.95" customHeight="1">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -13268,7 +13274,7 @@
       <c r="AJ307" s="1"/>
       <c r="AK307" s="1"/>
     </row>
-    <row r="308" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:37" ht="15.95" customHeight="1">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -13307,7 +13313,7 @@
       <c r="AJ308" s="1"/>
       <c r="AK308" s="1"/>
     </row>
-    <row r="309" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:37" ht="15.95" customHeight="1">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -13346,7 +13352,7 @@
       <c r="AJ309" s="1"/>
       <c r="AK309" s="1"/>
     </row>
-    <row r="310" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:37" ht="15.95" customHeight="1">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -13385,7 +13391,7 @@
       <c r="AJ310" s="1"/>
       <c r="AK310" s="1"/>
     </row>
-    <row r="311" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:37" ht="15.95" customHeight="1">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -13424,7 +13430,7 @@
       <c r="AJ311" s="1"/>
       <c r="AK311" s="1"/>
     </row>
-    <row r="312" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:37" ht="15.95" customHeight="1">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -13463,7 +13469,7 @@
       <c r="AJ312" s="1"/>
       <c r="AK312" s="1"/>
     </row>
-    <row r="313" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:37" ht="15.95" customHeight="1">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -13502,7 +13508,7 @@
       <c r="AJ313" s="1"/>
       <c r="AK313" s="1"/>
     </row>
-    <row r="314" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:37" ht="15.95" customHeight="1">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -13541,7 +13547,7 @@
       <c r="AJ314" s="1"/>
       <c r="AK314" s="1"/>
     </row>
-    <row r="315" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:37" ht="15.95" customHeight="1">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -13580,7 +13586,7 @@
       <c r="AJ315" s="1"/>
       <c r="AK315" s="1"/>
     </row>
-    <row r="316" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:37" ht="15.95" customHeight="1">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -13619,7 +13625,7 @@
       <c r="AJ316" s="1"/>
       <c r="AK316" s="1"/>
     </row>
-    <row r="317" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:37" ht="15.95" customHeight="1">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -13658,7 +13664,7 @@
       <c r="AJ317" s="1"/>
       <c r="AK317" s="1"/>
     </row>
-    <row r="318" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:37" ht="15.95" customHeight="1">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -13697,7 +13703,7 @@
       <c r="AJ318" s="1"/>
       <c r="AK318" s="1"/>
     </row>
-    <row r="319" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:37" ht="15.95" customHeight="1">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -13736,7 +13742,7 @@
       <c r="AJ319" s="1"/>
       <c r="AK319" s="1"/>
     </row>
-    <row r="320" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:37" ht="15.95" customHeight="1">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -13775,7 +13781,7 @@
       <c r="AJ320" s="1"/>
       <c r="AK320" s="1"/>
     </row>
-    <row r="321" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:37" ht="15.95" customHeight="1">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -13814,7 +13820,7 @@
       <c r="AJ321" s="1"/>
       <c r="AK321" s="1"/>
     </row>
-    <row r="322" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:37" ht="15.95" customHeight="1">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -13853,7 +13859,7 @@
       <c r="AJ322" s="1"/>
       <c r="AK322" s="1"/>
     </row>
-    <row r="323" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:37" ht="15.95" customHeight="1">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -13892,7 +13898,7 @@
       <c r="AJ323" s="1"/>
       <c r="AK323" s="1"/>
     </row>
-    <row r="324" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:37" ht="15.95" customHeight="1">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -13931,7 +13937,7 @@
       <c r="AJ324" s="1"/>
       <c r="AK324" s="1"/>
     </row>
-    <row r="325" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:37" ht="15.95" customHeight="1">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -13970,7 +13976,7 @@
       <c r="AJ325" s="1"/>
       <c r="AK325" s="1"/>
     </row>
-    <row r="326" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:37" ht="15.95" customHeight="1">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -14009,7 +14015,7 @@
       <c r="AJ326" s="1"/>
       <c r="AK326" s="1"/>
     </row>
-    <row r="327" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:37" ht="15.95" customHeight="1">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -14048,7 +14054,7 @@
       <c r="AJ327" s="1"/>
       <c r="AK327" s="1"/>
     </row>
-    <row r="328" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:37" ht="15.95" customHeight="1">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -14087,7 +14093,7 @@
       <c r="AJ328" s="1"/>
       <c r="AK328" s="1"/>
     </row>
-    <row r="329" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:37" ht="15.95" customHeight="1">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -14126,7 +14132,7 @@
       <c r="AJ329" s="1"/>
       <c r="AK329" s="1"/>
     </row>
-    <row r="330" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:37" ht="15.95" customHeight="1">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -14165,7 +14171,7 @@
       <c r="AJ330" s="1"/>
       <c r="AK330" s="1"/>
     </row>
-    <row r="331" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:37" ht="15.95" customHeight="1">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -14204,7 +14210,7 @@
       <c r="AJ331" s="1"/>
       <c r="AK331" s="1"/>
     </row>
-    <row r="332" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:37" ht="15.95" customHeight="1">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -14243,7 +14249,7 @@
       <c r="AJ332" s="1"/>
       <c r="AK332" s="1"/>
     </row>
-    <row r="333" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:37" ht="15.95" customHeight="1">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -14282,7 +14288,7 @@
       <c r="AJ333" s="1"/>
       <c r="AK333" s="1"/>
     </row>
-    <row r="334" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:37" ht="15.95" customHeight="1">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -14321,7 +14327,7 @@
       <c r="AJ334" s="1"/>
       <c r="AK334" s="1"/>
     </row>
-    <row r="335" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:37" ht="15.95" customHeight="1">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -14360,7 +14366,7 @@
       <c r="AJ335" s="1"/>
       <c r="AK335" s="1"/>
     </row>
-    <row r="336" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:37" ht="15.95" customHeight="1">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -14399,7 +14405,7 @@
       <c r="AJ336" s="1"/>
       <c r="AK336" s="1"/>
     </row>
-    <row r="337" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:37" ht="15.95" customHeight="1">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -14438,7 +14444,7 @@
       <c r="AJ337" s="1"/>
       <c r="AK337" s="1"/>
     </row>
-    <row r="338" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:37" ht="15.95" customHeight="1">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -14477,7 +14483,7 @@
       <c r="AJ338" s="1"/>
       <c r="AK338" s="1"/>
     </row>
-    <row r="339" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:37" ht="15.95" customHeight="1">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -14516,7 +14522,7 @@
       <c r="AJ339" s="1"/>
       <c r="AK339" s="1"/>
     </row>
-    <row r="340" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:37" ht="15.95" customHeight="1">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -14555,7 +14561,7 @@
       <c r="AJ340" s="1"/>
       <c r="AK340" s="1"/>
     </row>
-    <row r="341" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:37" ht="15.95" customHeight="1">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -14594,7 +14600,7 @@
       <c r="AJ341" s="1"/>
       <c r="AK341" s="1"/>
     </row>
-    <row r="342" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:37" ht="15.95" customHeight="1">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -14633,7 +14639,7 @@
       <c r="AJ342" s="1"/>
       <c r="AK342" s="1"/>
     </row>
-    <row r="343" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:37" ht="15.95" customHeight="1">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -14672,7 +14678,7 @@
       <c r="AJ343" s="1"/>
       <c r="AK343" s="1"/>
     </row>
-    <row r="344" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:37" ht="15.95" customHeight="1">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -14711,7 +14717,7 @@
       <c r="AJ344" s="1"/>
       <c r="AK344" s="1"/>
     </row>
-    <row r="345" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:37" ht="15.95" customHeight="1">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -14750,7 +14756,7 @@
       <c r="AJ345" s="1"/>
       <c r="AK345" s="1"/>
     </row>
-    <row r="346" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:37" ht="15.95" customHeight="1">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -14789,7 +14795,7 @@
       <c r="AJ346" s="1"/>
       <c r="AK346" s="1"/>
     </row>
-    <row r="347" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:37" ht="15.95" customHeight="1">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -14828,7 +14834,7 @@
       <c r="AJ347" s="1"/>
       <c r="AK347" s="1"/>
     </row>
-    <row r="348" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:37" ht="15.95" customHeight="1">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -14867,7 +14873,7 @@
       <c r="AJ348" s="1"/>
       <c r="AK348" s="1"/>
     </row>
-    <row r="349" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:37" ht="15.95" customHeight="1">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -14906,7 +14912,7 @@
       <c r="AJ349" s="1"/>
       <c r="AK349" s="1"/>
     </row>
-    <row r="350" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:37" ht="15.95" customHeight="1">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -14945,7 +14951,7 @@
       <c r="AJ350" s="1"/>
       <c r="AK350" s="1"/>
     </row>
-    <row r="351" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:37" ht="15.95" customHeight="1">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -14984,7 +14990,7 @@
       <c r="AJ351" s="1"/>
       <c r="AK351" s="1"/>
     </row>
-    <row r="352" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:37" ht="15.95" customHeight="1">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -15023,7 +15029,7 @@
       <c r="AJ352" s="1"/>
       <c r="AK352" s="1"/>
     </row>
-    <row r="353" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:37" ht="15.95" customHeight="1">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -15062,7 +15068,7 @@
       <c r="AJ353" s="1"/>
       <c r="AK353" s="1"/>
     </row>
-    <row r="354" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:37" ht="15.95" customHeight="1">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -15101,7 +15107,7 @@
       <c r="AJ354" s="1"/>
       <c r="AK354" s="1"/>
     </row>
-    <row r="355" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:37" ht="15.95" customHeight="1">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -15140,7 +15146,7 @@
       <c r="AJ355" s="1"/>
       <c r="AK355" s="1"/>
     </row>
-    <row r="356" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:37" ht="15.95" customHeight="1">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -15179,7 +15185,7 @@
       <c r="AJ356" s="1"/>
       <c r="AK356" s="1"/>
     </row>
-    <row r="357" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:37" ht="15.95" customHeight="1">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -15218,7 +15224,7 @@
       <c r="AJ357" s="1"/>
       <c r="AK357" s="1"/>
     </row>
-    <row r="358" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:37" ht="15.95" customHeight="1">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -15257,7 +15263,7 @@
       <c r="AJ358" s="1"/>
       <c r="AK358" s="1"/>
     </row>
-    <row r="359" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:37" ht="15.95" customHeight="1">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -15296,7 +15302,7 @@
       <c r="AJ359" s="1"/>
       <c r="AK359" s="1"/>
     </row>
-    <row r="360" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:37" ht="15.95" customHeight="1">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -15335,7 +15341,7 @@
       <c r="AJ360" s="1"/>
       <c r="AK360" s="1"/>
     </row>
-    <row r="361" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:37" ht="15.95" customHeight="1">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -15374,7 +15380,7 @@
       <c r="AJ361" s="1"/>
       <c r="AK361" s="1"/>
     </row>
-    <row r="362" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:37" ht="15.95" customHeight="1">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -15413,7 +15419,7 @@
       <c r="AJ362" s="1"/>
       <c r="AK362" s="1"/>
     </row>
-    <row r="363" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:37" ht="15.95" customHeight="1">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -15452,7 +15458,7 @@
       <c r="AJ363" s="1"/>
       <c r="AK363" s="1"/>
     </row>
-    <row r="364" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:37" ht="15.95" customHeight="1">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -15491,7 +15497,7 @@
       <c r="AJ364" s="1"/>
       <c r="AK364" s="1"/>
     </row>
-    <row r="365" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:37" ht="15.95" customHeight="1">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -15530,7 +15536,7 @@
       <c r="AJ365" s="1"/>
       <c r="AK365" s="1"/>
     </row>
-    <row r="366" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:37" ht="15.95" customHeight="1">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -15569,7 +15575,7 @@
       <c r="AJ366" s="1"/>
       <c r="AK366" s="1"/>
     </row>
-    <row r="367" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:37" ht="15.95" customHeight="1">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -15608,7 +15614,7 @@
       <c r="AJ367" s="1"/>
       <c r="AK367" s="1"/>
     </row>
-    <row r="368" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:37" ht="15.95" customHeight="1">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -15647,7 +15653,7 @@
       <c r="AJ368" s="1"/>
       <c r="AK368" s="1"/>
     </row>
-    <row r="369" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:37" ht="15.95" customHeight="1">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -15686,7 +15692,7 @@
       <c r="AJ369" s="1"/>
       <c r="AK369" s="1"/>
     </row>
-    <row r="370" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:37" ht="15.95" customHeight="1">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -15725,7 +15731,7 @@
       <c r="AJ370" s="1"/>
       <c r="AK370" s="1"/>
     </row>
-    <row r="371" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:37" ht="15.95" customHeight="1">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -15764,7 +15770,7 @@
       <c r="AJ371" s="1"/>
       <c r="AK371" s="1"/>
     </row>
-    <row r="372" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:37" ht="15.95" customHeight="1">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -15803,7 +15809,7 @@
       <c r="AJ372" s="1"/>
       <c r="AK372" s="1"/>
     </row>
-    <row r="373" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:37" ht="15.95" customHeight="1">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -15842,7 +15848,7 @@
       <c r="AJ373" s="1"/>
       <c r="AK373" s="1"/>
     </row>
-    <row r="374" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:37" ht="15.95" customHeight="1">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -15881,7 +15887,7 @@
       <c r="AJ374" s="1"/>
       <c r="AK374" s="1"/>
     </row>
-    <row r="375" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:37" ht="15.95" customHeight="1">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -15920,7 +15926,7 @@
       <c r="AJ375" s="1"/>
       <c r="AK375" s="1"/>
     </row>
-    <row r="376" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:37" ht="15.95" customHeight="1">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -15959,7 +15965,7 @@
       <c r="AJ376" s="1"/>
       <c r="AK376" s="1"/>
     </row>
-    <row r="377" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:37" ht="15.95" customHeight="1">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -15998,7 +16004,7 @@
       <c r="AJ377" s="1"/>
       <c r="AK377" s="1"/>
     </row>
-    <row r="378" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:37" ht="15.95" customHeight="1">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -16037,7 +16043,7 @@
       <c r="AJ378" s="1"/>
       <c r="AK378" s="1"/>
     </row>
-    <row r="379" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:37" ht="15.95" customHeight="1">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -16076,7 +16082,7 @@
       <c r="AJ379" s="1"/>
       <c r="AK379" s="1"/>
     </row>
-    <row r="380" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:37" ht="15.95" customHeight="1">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -16115,7 +16121,7 @@
       <c r="AJ380" s="1"/>
       <c r="AK380" s="1"/>
     </row>
-    <row r="381" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:37" ht="15.95" customHeight="1">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -16154,7 +16160,7 @@
       <c r="AJ381" s="1"/>
       <c r="AK381" s="1"/>
     </row>
-    <row r="382" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:37" ht="15.95" customHeight="1">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -16193,7 +16199,7 @@
       <c r="AJ382" s="1"/>
       <c r="AK382" s="1"/>
     </row>
-    <row r="383" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:37" ht="15.95" customHeight="1">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -16232,7 +16238,7 @@
       <c r="AJ383" s="1"/>
       <c r="AK383" s="1"/>
     </row>
-    <row r="384" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:37" ht="15.95" customHeight="1">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -16271,7 +16277,7 @@
       <c r="AJ384" s="1"/>
       <c r="AK384" s="1"/>
     </row>
-    <row r="385" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:37" ht="15.95" customHeight="1">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -16310,7 +16316,7 @@
       <c r="AJ385" s="1"/>
       <c r="AK385" s="1"/>
     </row>
-    <row r="386" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:37" ht="15.95" customHeight="1">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -16349,7 +16355,7 @@
       <c r="AJ386" s="1"/>
       <c r="AK386" s="1"/>
     </row>
-    <row r="387" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:37" ht="15.95" customHeight="1">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -16388,7 +16394,7 @@
       <c r="AJ387" s="1"/>
       <c r="AK387" s="1"/>
     </row>
-    <row r="388" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:37" ht="15.95" customHeight="1">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -16427,7 +16433,7 @@
       <c r="AJ388" s="1"/>
       <c r="AK388" s="1"/>
     </row>
-    <row r="389" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:37" ht="15.95" customHeight="1">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -16466,7 +16472,7 @@
       <c r="AJ389" s="1"/>
       <c r="AK389" s="1"/>
     </row>
-    <row r="390" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:37" ht="15.95" customHeight="1">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -16505,7 +16511,7 @@
       <c r="AJ390" s="1"/>
       <c r="AK390" s="1"/>
     </row>
-    <row r="391" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:37" ht="15.95" customHeight="1">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -16544,7 +16550,7 @@
       <c r="AJ391" s="1"/>
       <c r="AK391" s="1"/>
     </row>
-    <row r="392" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:37" ht="15.95" customHeight="1">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -16583,7 +16589,7 @@
       <c r="AJ392" s="1"/>
       <c r="AK392" s="1"/>
     </row>
-    <row r="393" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:37" ht="15.95" customHeight="1">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -16622,7 +16628,7 @@
       <c r="AJ393" s="1"/>
       <c r="AK393" s="1"/>
     </row>
-    <row r="394" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:37" ht="15.95" customHeight="1">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -16661,7 +16667,7 @@
       <c r="AJ394" s="1"/>
       <c r="AK394" s="1"/>
     </row>
-    <row r="395" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:37" ht="15.95" customHeight="1">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -16700,7 +16706,7 @@
       <c r="AJ395" s="1"/>
       <c r="AK395" s="1"/>
     </row>
-    <row r="396" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:37" ht="15.95" customHeight="1">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -16739,7 +16745,7 @@
       <c r="AJ396" s="1"/>
       <c r="AK396" s="1"/>
     </row>
-    <row r="397" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:37" ht="15.95" customHeight="1">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -16778,7 +16784,7 @@
       <c r="AJ397" s="1"/>
       <c r="AK397" s="1"/>
     </row>
-    <row r="398" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:37" ht="15.95" customHeight="1">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -16817,7 +16823,7 @@
       <c r="AJ398" s="1"/>
       <c r="AK398" s="1"/>
     </row>
-    <row r="399" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:37" ht="15.95" customHeight="1">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -16856,7 +16862,7 @@
       <c r="AJ399" s="1"/>
       <c r="AK399" s="1"/>
     </row>
-    <row r="400" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:37" ht="15.95" customHeight="1">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -16895,7 +16901,7 @@
       <c r="AJ400" s="1"/>
       <c r="AK400" s="1"/>
     </row>
-    <row r="401" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:37" ht="15.95" customHeight="1">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -16934,7 +16940,7 @@
       <c r="AJ401" s="1"/>
       <c r="AK401" s="1"/>
     </row>
-    <row r="402" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:37" ht="15.95" customHeight="1">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -16973,7 +16979,7 @@
       <c r="AJ402" s="1"/>
       <c r="AK402" s="1"/>
     </row>
-    <row r="403" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:37" ht="15.95" customHeight="1">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -17012,7 +17018,7 @@
       <c r="AJ403" s="1"/>
       <c r="AK403" s="1"/>
     </row>
-    <row r="404" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:37" ht="15.95" customHeight="1">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -17051,7 +17057,7 @@
       <c r="AJ404" s="1"/>
       <c r="AK404" s="1"/>
     </row>
-    <row r="405" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:37" ht="15.95" customHeight="1">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -17090,7 +17096,7 @@
       <c r="AJ405" s="1"/>
       <c r="AK405" s="1"/>
     </row>
-    <row r="406" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:37" ht="15.95" customHeight="1">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -17129,7 +17135,7 @@
       <c r="AJ406" s="1"/>
       <c r="AK406" s="1"/>
     </row>
-    <row r="407" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:37" ht="15.95" customHeight="1">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -17168,7 +17174,7 @@
       <c r="AJ407" s="1"/>
       <c r="AK407" s="1"/>
     </row>
-    <row r="408" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:37" ht="15.95" customHeight="1">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -17207,7 +17213,7 @@
       <c r="AJ408" s="1"/>
       <c r="AK408" s="1"/>
     </row>
-    <row r="409" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:37" ht="15.95" customHeight="1">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -17246,7 +17252,7 @@
       <c r="AJ409" s="1"/>
       <c r="AK409" s="1"/>
     </row>
-    <row r="410" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:37" ht="15.95" customHeight="1">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -17285,7 +17291,7 @@
       <c r="AJ410" s="1"/>
       <c r="AK410" s="1"/>
     </row>
-    <row r="411" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:37" ht="15.95" customHeight="1">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -17324,7 +17330,7 @@
       <c r="AJ411" s="1"/>
       <c r="AK411" s="1"/>
     </row>
-    <row r="412" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:37" ht="15.95" customHeight="1">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -17363,7 +17369,7 @@
       <c r="AJ412" s="1"/>
       <c r="AK412" s="1"/>
     </row>
-    <row r="413" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:37" ht="15.95" customHeight="1">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -17402,7 +17408,7 @@
       <c r="AJ413" s="1"/>
       <c r="AK413" s="1"/>
     </row>
-    <row r="414" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:37" ht="15.95" customHeight="1">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -17441,7 +17447,7 @@
       <c r="AJ414" s="1"/>
       <c r="AK414" s="1"/>
     </row>
-    <row r="415" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:37" ht="15.95" customHeight="1">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -17480,7 +17486,7 @@
       <c r="AJ415" s="1"/>
       <c r="AK415" s="1"/>
     </row>
-    <row r="416" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:37" ht="15.95" customHeight="1">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -17519,7 +17525,7 @@
       <c r="AJ416" s="1"/>
       <c r="AK416" s="1"/>
     </row>
-    <row r="417" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:37" ht="15.95" customHeight="1">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -17558,7 +17564,7 @@
       <c r="AJ417" s="1"/>
       <c r="AK417" s="1"/>
     </row>
-    <row r="418" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:37" ht="15.95" customHeight="1">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -17597,7 +17603,7 @@
       <c r="AJ418" s="1"/>
       <c r="AK418" s="1"/>
     </row>
-    <row r="419" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:37" ht="15.95" customHeight="1">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -17636,7 +17642,7 @@
       <c r="AJ419" s="1"/>
       <c r="AK419" s="1"/>
     </row>
-    <row r="420" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:37" ht="15.95" customHeight="1">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -17675,7 +17681,7 @@
       <c r="AJ420" s="1"/>
       <c r="AK420" s="1"/>
     </row>
-    <row r="421" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:37" ht="15.95" customHeight="1">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -17714,7 +17720,7 @@
       <c r="AJ421" s="1"/>
       <c r="AK421" s="1"/>
     </row>
-    <row r="422" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:37" ht="15.95" customHeight="1">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -17753,7 +17759,7 @@
       <c r="AJ422" s="1"/>
       <c r="AK422" s="1"/>
     </row>
-    <row r="423" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:37" ht="15.95" customHeight="1">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -17792,7 +17798,7 @@
       <c r="AJ423" s="1"/>
       <c r="AK423" s="1"/>
     </row>
-    <row r="424" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:37" ht="15.95" customHeight="1">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -17831,7 +17837,7 @@
       <c r="AJ424" s="1"/>
       <c r="AK424" s="1"/>
     </row>
-    <row r="425" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:37" ht="15.95" customHeight="1">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -17870,7 +17876,7 @@
       <c r="AJ425" s="1"/>
       <c r="AK425" s="1"/>
     </row>
-    <row r="426" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:37" ht="15.95" customHeight="1">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -17909,7 +17915,7 @@
       <c r="AJ426" s="1"/>
       <c r="AK426" s="1"/>
     </row>
-    <row r="427" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:37" ht="15.95" customHeight="1">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -17948,7 +17954,7 @@
       <c r="AJ427" s="1"/>
       <c r="AK427" s="1"/>
     </row>
-    <row r="428" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:37" ht="15.95" customHeight="1">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -17987,7 +17993,7 @@
       <c r="AJ428" s="1"/>
       <c r="AK428" s="1"/>
     </row>
-    <row r="429" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:37" ht="15.95" customHeight="1">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -18026,7 +18032,7 @@
       <c r="AJ429" s="1"/>
       <c r="AK429" s="1"/>
     </row>
-    <row r="430" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:37" ht="15.95" customHeight="1">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -18065,7 +18071,7 @@
       <c r="AJ430" s="1"/>
       <c r="AK430" s="1"/>
     </row>
-    <row r="431" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:37" ht="15.95" customHeight="1">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -18104,7 +18110,7 @@
       <c r="AJ431" s="1"/>
       <c r="AK431" s="1"/>
     </row>
-    <row r="432" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:37" ht="15.95" customHeight="1">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -18143,7 +18149,7 @@
       <c r="AJ432" s="1"/>
       <c r="AK432" s="1"/>
     </row>
-    <row r="433" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:37" ht="15.95" customHeight="1">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -18182,7 +18188,7 @@
       <c r="AJ433" s="1"/>
       <c r="AK433" s="1"/>
     </row>
-    <row r="434" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:37" ht="15.95" customHeight="1">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -18221,7 +18227,7 @@
       <c r="AJ434" s="1"/>
       <c r="AK434" s="1"/>
     </row>
-    <row r="435" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:37" ht="15.95" customHeight="1">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -18260,7 +18266,7 @@
       <c r="AJ435" s="1"/>
       <c r="AK435" s="1"/>
     </row>
-    <row r="436" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:37" ht="15.95" customHeight="1">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -18299,7 +18305,7 @@
       <c r="AJ436" s="1"/>
       <c r="AK436" s="1"/>
     </row>
-    <row r="437" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:37" ht="15.95" customHeight="1">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -18338,7 +18344,7 @@
       <c r="AJ437" s="1"/>
       <c r="AK437" s="1"/>
     </row>
-    <row r="438" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:37" ht="15.95" customHeight="1">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -18377,7 +18383,7 @@
       <c r="AJ438" s="1"/>
       <c r="AK438" s="1"/>
     </row>
-    <row r="439" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:37" ht="15.95" customHeight="1">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -18416,7 +18422,7 @@
       <c r="AJ439" s="1"/>
       <c r="AK439" s="1"/>
     </row>
-    <row r="440" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:37" ht="15.95" customHeight="1">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -18455,7 +18461,7 @@
       <c r="AJ440" s="1"/>
       <c r="AK440" s="1"/>
     </row>
-    <row r="441" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:37" ht="15.95" customHeight="1">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -18494,7 +18500,7 @@
       <c r="AJ441" s="1"/>
       <c r="AK441" s="1"/>
     </row>
-    <row r="442" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:37" ht="15.95" customHeight="1">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -18533,7 +18539,7 @@
       <c r="AJ442" s="1"/>
       <c r="AK442" s="1"/>
     </row>
-    <row r="443" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:37" ht="15.95" customHeight="1">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -18572,7 +18578,7 @@
       <c r="AJ443" s="1"/>
       <c r="AK443" s="1"/>
     </row>
-    <row r="444" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:37" ht="15.95" customHeight="1">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -18611,7 +18617,7 @@
       <c r="AJ444" s="1"/>
       <c r="AK444" s="1"/>
     </row>
-    <row r="445" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:37" ht="15.95" customHeight="1">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -18650,7 +18656,7 @@
       <c r="AJ445" s="1"/>
       <c r="AK445" s="1"/>
     </row>
-    <row r="446" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:37" ht="15.95" customHeight="1">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -18689,7 +18695,7 @@
       <c r="AJ446" s="1"/>
       <c r="AK446" s="1"/>
     </row>
-    <row r="447" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:37" ht="15.95" customHeight="1">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -18728,7 +18734,7 @@
       <c r="AJ447" s="1"/>
       <c r="AK447" s="1"/>
     </row>
-    <row r="448" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:37" ht="15.95" customHeight="1">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -18767,7 +18773,7 @@
       <c r="AJ448" s="1"/>
       <c r="AK448" s="1"/>
     </row>
-    <row r="449" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:37" ht="15.95" customHeight="1">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -18806,7 +18812,7 @@
       <c r="AJ449" s="1"/>
       <c r="AK449" s="1"/>
     </row>
-    <row r="450" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:37" ht="15.95" customHeight="1">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -18845,7 +18851,7 @@
       <c r="AJ450" s="1"/>
       <c r="AK450" s="1"/>
     </row>
-    <row r="451" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:37" ht="15.95" customHeight="1">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -18884,7 +18890,7 @@
       <c r="AJ451" s="1"/>
       <c r="AK451" s="1"/>
     </row>
-    <row r="452" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:37" ht="15.95" customHeight="1">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -18923,7 +18929,7 @@
       <c r="AJ452" s="1"/>
       <c r="AK452" s="1"/>
     </row>
-    <row r="453" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:37" ht="15.95" customHeight="1">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -18962,7 +18968,7 @@
       <c r="AJ453" s="1"/>
       <c r="AK453" s="1"/>
     </row>
-    <row r="454" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:37" ht="15.95" customHeight="1">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -19001,7 +19007,7 @@
       <c r="AJ454" s="1"/>
       <c r="AK454" s="1"/>
     </row>
-    <row r="455" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:37" ht="15.95" customHeight="1">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -19040,7 +19046,7 @@
       <c r="AJ455" s="1"/>
       <c r="AK455" s="1"/>
     </row>
-    <row r="456" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:37" ht="15.95" customHeight="1">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -19079,7 +19085,7 @@
       <c r="AJ456" s="1"/>
       <c r="AK456" s="1"/>
     </row>
-    <row r="457" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:37" ht="15.95" customHeight="1">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -19118,7 +19124,7 @@
       <c r="AJ457" s="1"/>
       <c r="AK457" s="1"/>
     </row>
-    <row r="458" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:37" ht="15.95" customHeight="1">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -19157,7 +19163,7 @@
       <c r="AJ458" s="1"/>
       <c r="AK458" s="1"/>
     </row>
-    <row r="459" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:37" ht="15.95" customHeight="1">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -19196,7 +19202,7 @@
       <c r="AJ459" s="1"/>
       <c r="AK459" s="1"/>
     </row>
-    <row r="460" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:37" ht="15.95" customHeight="1">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -19235,7 +19241,7 @@
       <c r="AJ460" s="1"/>
       <c r="AK460" s="1"/>
     </row>
-    <row r="461" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:37" ht="15.95" customHeight="1">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -19274,7 +19280,7 @@
       <c r="AJ461" s="1"/>
       <c r="AK461" s="1"/>
     </row>
-    <row r="462" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:37" ht="15.95" customHeight="1">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -19313,7 +19319,7 @@
       <c r="AJ462" s="1"/>
       <c r="AK462" s="1"/>
     </row>
-    <row r="463" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:37" ht="15.95" customHeight="1">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -19352,7 +19358,7 @@
       <c r="AJ463" s="1"/>
       <c r="AK463" s="1"/>
     </row>
-    <row r="464" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:37" ht="15.95" customHeight="1">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -19391,7 +19397,7 @@
       <c r="AJ464" s="1"/>
       <c r="AK464" s="1"/>
     </row>
-    <row r="465" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:37" ht="15.95" customHeight="1">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -19430,7 +19436,7 @@
       <c r="AJ465" s="1"/>
       <c r="AK465" s="1"/>
     </row>
-    <row r="466" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:37" ht="15.95" customHeight="1">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -19469,7 +19475,7 @@
       <c r="AJ466" s="1"/>
       <c r="AK466" s="1"/>
     </row>
-    <row r="467" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:37" ht="15.95" customHeight="1">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -19508,7 +19514,7 @@
       <c r="AJ467" s="1"/>
       <c r="AK467" s="1"/>
     </row>
-    <row r="468" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:37" ht="15.95" customHeight="1">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -19547,7 +19553,7 @@
       <c r="AJ468" s="1"/>
       <c r="AK468" s="1"/>
     </row>
-    <row r="469" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:37" ht="15.95" customHeight="1">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -19586,7 +19592,7 @@
       <c r="AJ469" s="1"/>
       <c r="AK469" s="1"/>
     </row>
-    <row r="470" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:37" ht="15.95" customHeight="1">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -19625,7 +19631,7 @@
       <c r="AJ470" s="1"/>
       <c r="AK470" s="1"/>
     </row>
-    <row r="471" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:37" ht="15.95" customHeight="1">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -19664,7 +19670,7 @@
       <c r="AJ471" s="1"/>
       <c r="AK471" s="1"/>
     </row>
-    <row r="472" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:37" ht="15.95" customHeight="1">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -19703,7 +19709,7 @@
       <c r="AJ472" s="1"/>
       <c r="AK472" s="1"/>
     </row>
-    <row r="473" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:37" ht="15.95" customHeight="1">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -19742,7 +19748,7 @@
       <c r="AJ473" s="1"/>
       <c r="AK473" s="1"/>
     </row>
-    <row r="474" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:37" ht="15.95" customHeight="1">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -19781,7 +19787,7 @@
       <c r="AJ474" s="1"/>
       <c r="AK474" s="1"/>
     </row>
-    <row r="475" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:37" ht="15.95" customHeight="1">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -19820,7 +19826,7 @@
       <c r="AJ475" s="1"/>
       <c r="AK475" s="1"/>
     </row>
-    <row r="476" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:37" ht="15.95" customHeight="1">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -19859,7 +19865,7 @@
       <c r="AJ476" s="1"/>
       <c r="AK476" s="1"/>
     </row>
-    <row r="477" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:37" ht="15.95" customHeight="1">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -19898,7 +19904,7 @@
       <c r="AJ477" s="1"/>
       <c r="AK477" s="1"/>
     </row>
-    <row r="478" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:37" ht="15.95" customHeight="1">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -19937,7 +19943,7 @@
       <c r="AJ478" s="1"/>
       <c r="AK478" s="1"/>
     </row>
-    <row r="479" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:37" ht="15.95" customHeight="1">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -19976,7 +19982,7 @@
       <c r="AJ479" s="1"/>
       <c r="AK479" s="1"/>
     </row>
-    <row r="480" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:37" ht="15.95" customHeight="1">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -20015,7 +20021,7 @@
       <c r="AJ480" s="1"/>
       <c r="AK480" s="1"/>
     </row>
-    <row r="481" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:37" ht="15.95" customHeight="1">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -20054,7 +20060,7 @@
       <c r="AJ481" s="1"/>
       <c r="AK481" s="1"/>
     </row>
-    <row r="482" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:37" ht="15.95" customHeight="1">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -20093,7 +20099,7 @@
       <c r="AJ482" s="1"/>
       <c r="AK482" s="1"/>
     </row>
-    <row r="483" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:37" ht="15.95" customHeight="1">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -20132,7 +20138,7 @@
       <c r="AJ483" s="1"/>
       <c r="AK483" s="1"/>
     </row>
-    <row r="484" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:37" ht="15.95" customHeight="1">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -20171,7 +20177,7 @@
       <c r="AJ484" s="1"/>
       <c r="AK484" s="1"/>
     </row>
-    <row r="485" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:37" ht="15.95" customHeight="1">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -20210,7 +20216,7 @@
       <c r="AJ485" s="1"/>
       <c r="AK485" s="1"/>
     </row>
-    <row r="486" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:37" ht="15.95" customHeight="1">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -20249,7 +20255,7 @@
       <c r="AJ486" s="1"/>
       <c r="AK486" s="1"/>
     </row>
-    <row r="487" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:37" ht="15.95" customHeight="1">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -20288,7 +20294,7 @@
       <c r="AJ487" s="1"/>
       <c r="AK487" s="1"/>
     </row>
-    <row r="488" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:37" ht="15.95" customHeight="1">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -20327,7 +20333,7 @@
       <c r="AJ488" s="1"/>
       <c r="AK488" s="1"/>
     </row>
-    <row r="489" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:37" ht="15.95" customHeight="1">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -20366,7 +20372,7 @@
       <c r="AJ489" s="1"/>
       <c r="AK489" s="1"/>
     </row>
-    <row r="490" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:37" ht="15.95" customHeight="1">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -20405,7 +20411,7 @@
       <c r="AJ490" s="1"/>
       <c r="AK490" s="1"/>
     </row>
-    <row r="491" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:37" ht="15.95" customHeight="1">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -20444,7 +20450,7 @@
       <c r="AJ491" s="1"/>
       <c r="AK491" s="1"/>
     </row>
-    <row r="492" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:37" ht="15.95" customHeight="1">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -20483,7 +20489,7 @@
       <c r="AJ492" s="1"/>
       <c r="AK492" s="1"/>
     </row>
-    <row r="493" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:37" ht="15.95" customHeight="1">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -20522,7 +20528,7 @@
       <c r="AJ493" s="1"/>
       <c r="AK493" s="1"/>
     </row>
-    <row r="494" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:37" ht="15.95" customHeight="1">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -20561,7 +20567,7 @@
       <c r="AJ494" s="1"/>
       <c r="AK494" s="1"/>
     </row>
-    <row r="495" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:37" ht="15.95" customHeight="1">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -20600,7 +20606,7 @@
       <c r="AJ495" s="1"/>
       <c r="AK495" s="1"/>
     </row>
-    <row r="496" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:37" ht="15.95" customHeight="1">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -20639,7 +20645,7 @@
       <c r="AJ496" s="1"/>
       <c r="AK496" s="1"/>
     </row>
-    <row r="497" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:37" ht="15.95" customHeight="1">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -20678,7 +20684,7 @@
       <c r="AJ497" s="1"/>
       <c r="AK497" s="1"/>
     </row>
-    <row r="498" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:37" ht="15.95" customHeight="1">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -20717,7 +20723,7 @@
       <c r="AJ498" s="1"/>
       <c r="AK498" s="1"/>
     </row>
-    <row r="499" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:37" ht="15.95" customHeight="1">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -20756,7 +20762,7 @@
       <c r="AJ499" s="1"/>
       <c r="AK499" s="1"/>
     </row>
-    <row r="500" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:37" ht="15.95" customHeight="1">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -20795,7 +20801,7 @@
       <c r="AJ500" s="1"/>
       <c r="AK500" s="1"/>
     </row>
-    <row r="501" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:37" ht="15.95" customHeight="1">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -20834,7 +20840,7 @@
       <c r="AJ501" s="1"/>
       <c r="AK501" s="1"/>
     </row>
-    <row r="502" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:37" ht="15.95" customHeight="1">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -20873,7 +20879,7 @@
       <c r="AJ502" s="1"/>
       <c r="AK502" s="1"/>
     </row>
-    <row r="503" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:37" ht="15.95" customHeight="1">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -20912,7 +20918,7 @@
       <c r="AJ503" s="1"/>
       <c r="AK503" s="1"/>
     </row>
-    <row r="504" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:37" ht="15.95" customHeight="1">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -20951,7 +20957,7 @@
       <c r="AJ504" s="1"/>
       <c r="AK504" s="1"/>
     </row>
-    <row r="505" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:37" ht="15.95" customHeight="1">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -20990,7 +20996,7 @@
       <c r="AJ505" s="1"/>
       <c r="AK505" s="1"/>
     </row>
-    <row r="506" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:37" ht="15.95" customHeight="1">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -21029,7 +21035,7 @@
       <c r="AJ506" s="1"/>
       <c r="AK506" s="1"/>
     </row>
-    <row r="507" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:37" ht="15.95" customHeight="1">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -21068,7 +21074,7 @@
       <c r="AJ507" s="1"/>
       <c r="AK507" s="1"/>
     </row>
-    <row r="508" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:37" ht="15.95" customHeight="1">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -21107,7 +21113,7 @@
       <c r="AJ508" s="1"/>
       <c r="AK508" s="1"/>
     </row>
-    <row r="509" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:37" ht="15.95" customHeight="1">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -21146,7 +21152,7 @@
       <c r="AJ509" s="1"/>
       <c r="AK509" s="1"/>
     </row>
-    <row r="510" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:37" ht="15.95" customHeight="1">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -21185,7 +21191,7 @@
       <c r="AJ510" s="1"/>
       <c r="AK510" s="1"/>
     </row>
-    <row r="511" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:37" ht="15.95" customHeight="1">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -21224,7 +21230,7 @@
       <c r="AJ511" s="1"/>
       <c r="AK511" s="1"/>
     </row>
-    <row r="512" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:37" ht="15.95" customHeight="1">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -21263,7 +21269,7 @@
       <c r="AJ512" s="1"/>
       <c r="AK512" s="1"/>
     </row>
-    <row r="513" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:37" ht="15.95" customHeight="1">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -21302,7 +21308,7 @@
       <c r="AJ513" s="1"/>
       <c r="AK513" s="1"/>
     </row>
-    <row r="514" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:37" ht="15.95" customHeight="1">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -21341,7 +21347,7 @@
       <c r="AJ514" s="1"/>
       <c r="AK514" s="1"/>
     </row>
-    <row r="515" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:37" ht="15.95" customHeight="1">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -21380,7 +21386,7 @@
       <c r="AJ515" s="1"/>
       <c r="AK515" s="1"/>
     </row>
-    <row r="516" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:37" ht="15.95" customHeight="1">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -21419,7 +21425,7 @@
       <c r="AJ516" s="1"/>
       <c r="AK516" s="1"/>
     </row>
-    <row r="517" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:37" ht="15.95" customHeight="1">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -21458,7 +21464,7 @@
       <c r="AJ517" s="1"/>
       <c r="AK517" s="1"/>
     </row>
-    <row r="518" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:37" ht="15.95" customHeight="1">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -21497,7 +21503,7 @@
       <c r="AJ518" s="1"/>
       <c r="AK518" s="1"/>
     </row>
-    <row r="519" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:37" ht="15.95" customHeight="1">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -21536,7 +21542,7 @@
       <c r="AJ519" s="1"/>
       <c r="AK519" s="1"/>
     </row>
-    <row r="520" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:37" ht="15.95" customHeight="1">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -21575,7 +21581,7 @@
       <c r="AJ520" s="1"/>
       <c r="AK520" s="1"/>
     </row>
-    <row r="521" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:37" ht="15.95" customHeight="1">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -21614,7 +21620,7 @@
       <c r="AJ521" s="1"/>
       <c r="AK521" s="1"/>
     </row>
-    <row r="522" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:37" ht="15.95" customHeight="1">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -21653,7 +21659,7 @@
       <c r="AJ522" s="1"/>
       <c r="AK522" s="1"/>
     </row>
-    <row r="523" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:37" ht="15.95" customHeight="1">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -21692,7 +21698,7 @@
       <c r="AJ523" s="1"/>
       <c r="AK523" s="1"/>
     </row>
-    <row r="524" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:37" ht="15.95" customHeight="1">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -21731,7 +21737,7 @@
       <c r="AJ524" s="1"/>
       <c r="AK524" s="1"/>
     </row>
-    <row r="525" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:37" ht="15.95" customHeight="1">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -21770,7 +21776,7 @@
       <c r="AJ525" s="1"/>
       <c r="AK525" s="1"/>
     </row>
-    <row r="526" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:37" ht="15.95" customHeight="1">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -21809,7 +21815,7 @@
       <c r="AJ526" s="1"/>
       <c r="AK526" s="1"/>
     </row>
-    <row r="527" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:37" ht="15.95" customHeight="1">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -21848,7 +21854,7 @@
       <c r="AJ527" s="1"/>
       <c r="AK527" s="1"/>
     </row>
-    <row r="528" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:37" ht="15.95" customHeight="1">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -21887,7 +21893,7 @@
       <c r="AJ528" s="1"/>
       <c r="AK528" s="1"/>
     </row>
-    <row r="529" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:37" ht="15.95" customHeight="1">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -21926,7 +21932,7 @@
       <c r="AJ529" s="1"/>
       <c r="AK529" s="1"/>
     </row>
-    <row r="530" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:37" ht="15.95" customHeight="1">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -21965,7 +21971,7 @@
       <c r="AJ530" s="1"/>
       <c r="AK530" s="1"/>
     </row>
-    <row r="531" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:37" ht="15.95" customHeight="1">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -22004,7 +22010,7 @@
       <c r="AJ531" s="1"/>
       <c r="AK531" s="1"/>
     </row>
-    <row r="532" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:37" ht="15.95" customHeight="1">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -22043,7 +22049,7 @@
       <c r="AJ532" s="1"/>
       <c r="AK532" s="1"/>
     </row>
-    <row r="533" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:37" ht="15.95" customHeight="1">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -22082,7 +22088,7 @@
       <c r="AJ533" s="1"/>
       <c r="AK533" s="1"/>
     </row>
-    <row r="534" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:37" ht="15.95" customHeight="1">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -22121,7 +22127,7 @@
       <c r="AJ534" s="1"/>
       <c r="AK534" s="1"/>
     </row>
-    <row r="535" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:37" ht="15.95" customHeight="1">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -22160,7 +22166,7 @@
       <c r="AJ535" s="1"/>
       <c r="AK535" s="1"/>
     </row>
-    <row r="536" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:37" ht="15.95" customHeight="1">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -22199,7 +22205,7 @@
       <c r="AJ536" s="1"/>
       <c r="AK536" s="1"/>
     </row>
-    <row r="537" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:37" ht="15.95" customHeight="1">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -22238,7 +22244,7 @@
       <c r="AJ537" s="1"/>
       <c r="AK537" s="1"/>
     </row>
-    <row r="538" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:37" ht="15.95" customHeight="1">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -22277,7 +22283,7 @@
       <c r="AJ538" s="1"/>
       <c r="AK538" s="1"/>
     </row>
-    <row r="539" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:37" ht="15.95" customHeight="1">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -22316,7 +22322,7 @@
       <c r="AJ539" s="1"/>
       <c r="AK539" s="1"/>
     </row>
-    <row r="540" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:37" ht="15.95" customHeight="1">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -22355,7 +22361,7 @@
       <c r="AJ540" s="1"/>
       <c r="AK540" s="1"/>
     </row>
-    <row r="541" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:37" ht="15.95" customHeight="1">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -22394,7 +22400,7 @@
       <c r="AJ541" s="1"/>
       <c r="AK541" s="1"/>
     </row>
-    <row r="542" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:37" ht="15.95" customHeight="1">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -22433,7 +22439,7 @@
       <c r="AJ542" s="1"/>
       <c r="AK542" s="1"/>
     </row>
-    <row r="543" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:37" ht="15.95" customHeight="1">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -22472,7 +22478,7 @@
       <c r="AJ543" s="1"/>
       <c r="AK543" s="1"/>
     </row>
-    <row r="544" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:37" ht="15.95" customHeight="1">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -22511,7 +22517,7 @@
       <c r="AJ544" s="1"/>
       <c r="AK544" s="1"/>
     </row>
-    <row r="545" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:37" ht="15.95" customHeight="1">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -22550,7 +22556,7 @@
       <c r="AJ545" s="1"/>
       <c r="AK545" s="1"/>
     </row>
-    <row r="546" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:37" ht="15.95" customHeight="1">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -22589,7 +22595,7 @@
       <c r="AJ546" s="1"/>
       <c r="AK546" s="1"/>
     </row>
-    <row r="547" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:37" ht="15.95" customHeight="1">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -22628,7 +22634,7 @@
       <c r="AJ547" s="1"/>
       <c r="AK547" s="1"/>
     </row>
-    <row r="548" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:37" ht="15.95" customHeight="1">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -22667,7 +22673,7 @@
       <c r="AJ548" s="1"/>
       <c r="AK548" s="1"/>
     </row>
-    <row r="549" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:37" ht="15.95" customHeight="1">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -22706,7 +22712,7 @@
       <c r="AJ549" s="1"/>
       <c r="AK549" s="1"/>
     </row>
-    <row r="550" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:37" ht="15.95" customHeight="1">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -22745,7 +22751,7 @@
       <c r="AJ550" s="1"/>
       <c r="AK550" s="1"/>
     </row>
-    <row r="551" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:37" ht="15.95" customHeight="1">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -22784,7 +22790,7 @@
       <c r="AJ551" s="1"/>
       <c r="AK551" s="1"/>
     </row>
-    <row r="552" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:37" ht="15.95" customHeight="1">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -22823,7 +22829,7 @@
       <c r="AJ552" s="1"/>
       <c r="AK552" s="1"/>
     </row>
-    <row r="553" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:37" ht="15.95" customHeight="1">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -22862,7 +22868,7 @@
       <c r="AJ553" s="1"/>
       <c r="AK553" s="1"/>
     </row>
-    <row r="554" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:37" ht="15.95" customHeight="1">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -22901,7 +22907,7 @@
       <c r="AJ554" s="1"/>
       <c r="AK554" s="1"/>
     </row>
-    <row r="555" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:37" ht="15.95" customHeight="1">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -22940,7 +22946,7 @@
       <c r="AJ555" s="1"/>
       <c r="AK555" s="1"/>
     </row>
-    <row r="556" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:37" ht="15.95" customHeight="1">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -22979,7 +22985,7 @@
       <c r="AJ556" s="1"/>
       <c r="AK556" s="1"/>
     </row>
-    <row r="557" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:37" ht="15.95" customHeight="1">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -23018,7 +23024,7 @@
       <c r="AJ557" s="1"/>
       <c r="AK557" s="1"/>
     </row>
-    <row r="558" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:37" ht="15.95" customHeight="1">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -23057,7 +23063,7 @@
       <c r="AJ558" s="1"/>
       <c r="AK558" s="1"/>
     </row>
-    <row r="559" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:37" ht="15.95" customHeight="1">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -23096,7 +23102,7 @@
       <c r="AJ559" s="1"/>
       <c r="AK559" s="1"/>
     </row>
-    <row r="560" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:37" ht="15.95" customHeight="1">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -23135,7 +23141,7 @@
       <c r="AJ560" s="1"/>
       <c r="AK560" s="1"/>
     </row>
-    <row r="561" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:37" ht="15.95" customHeight="1">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -23174,7 +23180,7 @@
       <c r="AJ561" s="1"/>
       <c r="AK561" s="1"/>
     </row>
-    <row r="562" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:37" ht="15.95" customHeight="1">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -23213,7 +23219,7 @@
       <c r="AJ562" s="1"/>
       <c r="AK562" s="1"/>
     </row>
-    <row r="563" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:37" ht="15.95" customHeight="1">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -23252,7 +23258,7 @@
       <c r="AJ563" s="1"/>
       <c r="AK563" s="1"/>
     </row>
-    <row r="564" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:37" ht="15.95" customHeight="1">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -23291,7 +23297,7 @@
       <c r="AJ564" s="1"/>
       <c r="AK564" s="1"/>
     </row>
-    <row r="565" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:37" ht="15.95" customHeight="1">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -23330,7 +23336,7 @@
       <c r="AJ565" s="1"/>
       <c r="AK565" s="1"/>
     </row>
-    <row r="566" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:37" ht="15.95" customHeight="1">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -23369,7 +23375,7 @@
       <c r="AJ566" s="1"/>
       <c r="AK566" s="1"/>
     </row>
-    <row r="567" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:37" ht="15.95" customHeight="1">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -23408,7 +23414,7 @@
       <c r="AJ567" s="1"/>
       <c r="AK567" s="1"/>
     </row>
-    <row r="568" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:37" ht="15.95" customHeight="1">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -23447,7 +23453,7 @@
       <c r="AJ568" s="1"/>
       <c r="AK568" s="1"/>
     </row>
-    <row r="569" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:37" ht="15.95" customHeight="1">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -23486,7 +23492,7 @@
       <c r="AJ569" s="1"/>
       <c r="AK569" s="1"/>
     </row>
-    <row r="570" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:37" ht="15.95" customHeight="1">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -23525,7 +23531,7 @@
       <c r="AJ570" s="1"/>
       <c r="AK570" s="1"/>
     </row>
-    <row r="571" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:37" ht="15.95" customHeight="1">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -23564,7 +23570,7 @@
       <c r="AJ571" s="1"/>
       <c r="AK571" s="1"/>
     </row>
-    <row r="572" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:37" ht="15.95" customHeight="1">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -23603,7 +23609,7 @@
       <c r="AJ572" s="1"/>
       <c r="AK572" s="1"/>
     </row>
-    <row r="573" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:37" ht="15.95" customHeight="1">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -23642,7 +23648,7 @@
       <c r="AJ573" s="1"/>
       <c r="AK573" s="1"/>
     </row>
-    <row r="574" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:37" ht="15.95" customHeight="1">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -23681,7 +23687,7 @@
       <c r="AJ574" s="1"/>
       <c r="AK574" s="1"/>
     </row>
-    <row r="575" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:37" ht="15.95" customHeight="1">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -23720,7 +23726,7 @@
       <c r="AJ575" s="1"/>
       <c r="AK575" s="1"/>
     </row>
-    <row r="576" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:37" ht="15.95" customHeight="1">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -23759,7 +23765,7 @@
       <c r="AJ576" s="1"/>
       <c r="AK576" s="1"/>
     </row>
-    <row r="577" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:37" ht="15.95" customHeight="1">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -23798,7 +23804,7 @@
       <c r="AJ577" s="1"/>
       <c r="AK577" s="1"/>
     </row>
-    <row r="578" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:37" ht="15.95" customHeight="1">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -23837,7 +23843,7 @@
       <c r="AJ578" s="1"/>
       <c r="AK578" s="1"/>
     </row>
-    <row r="579" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:37" ht="15.95" customHeight="1">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -23876,7 +23882,7 @@
       <c r="AJ579" s="1"/>
       <c r="AK579" s="1"/>
     </row>
-    <row r="580" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:37" ht="15.95" customHeight="1">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -23915,7 +23921,7 @@
       <c r="AJ580" s="1"/>
       <c r="AK580" s="1"/>
     </row>
-    <row r="581" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:37" ht="15.95" customHeight="1">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -23954,7 +23960,7 @@
       <c r="AJ581" s="1"/>
       <c r="AK581" s="1"/>
     </row>
-    <row r="582" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:37" ht="15.95" customHeight="1">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -23993,7 +23999,7 @@
       <c r="AJ582" s="1"/>
       <c r="AK582" s="1"/>
     </row>
-    <row r="583" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:37" ht="15.95" customHeight="1">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -24032,7 +24038,7 @@
       <c r="AJ583" s="1"/>
       <c r="AK583" s="1"/>
     </row>
-    <row r="584" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:37" ht="15.95" customHeight="1">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -24071,7 +24077,7 @@
       <c r="AJ584" s="1"/>
       <c r="AK584" s="1"/>
     </row>
-    <row r="585" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:37" ht="15.95" customHeight="1">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -24110,7 +24116,7 @@
       <c r="AJ585" s="1"/>
       <c r="AK585" s="1"/>
     </row>
-    <row r="586" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:37" ht="15.95" customHeight="1">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -24149,7 +24155,7 @@
       <c r="AJ586" s="1"/>
       <c r="AK586" s="1"/>
     </row>
-    <row r="587" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:37" ht="15.95" customHeight="1">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -24188,7 +24194,7 @@
       <c r="AJ587" s="1"/>
       <c r="AK587" s="1"/>
     </row>
-    <row r="588" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:37" ht="15.95" customHeight="1">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -24227,7 +24233,7 @@
       <c r="AJ588" s="1"/>
       <c r="AK588" s="1"/>
     </row>
-    <row r="589" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:37" ht="15.95" customHeight="1">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -24266,7 +24272,7 @@
       <c r="AJ589" s="1"/>
       <c r="AK589" s="1"/>
     </row>
-    <row r="590" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:37" ht="15.95" customHeight="1">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -24305,7 +24311,7 @@
       <c r="AJ590" s="1"/>
       <c r="AK590" s="1"/>
     </row>
-    <row r="591" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:37" ht="15.95" customHeight="1">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -24344,7 +24350,7 @@
       <c r="AJ591" s="1"/>
       <c r="AK591" s="1"/>
     </row>
-    <row r="592" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:37" ht="15.95" customHeight="1">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -24383,7 +24389,7 @@
       <c r="AJ592" s="1"/>
       <c r="AK592" s="1"/>
     </row>
-    <row r="593" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:37" ht="15.95" customHeight="1">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -24422,7 +24428,7 @@
       <c r="AJ593" s="1"/>
       <c r="AK593" s="1"/>
     </row>
-    <row r="594" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:37" ht="15.95" customHeight="1">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -24461,7 +24467,7 @@
       <c r="AJ594" s="1"/>
       <c r="AK594" s="1"/>
     </row>
-    <row r="595" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:37" ht="15.95" customHeight="1">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -24500,7 +24506,7 @@
       <c r="AJ595" s="1"/>
       <c r="AK595" s="1"/>
     </row>
-    <row r="596" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:37" ht="15.95" customHeight="1">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -24539,7 +24545,7 @@
       <c r="AJ596" s="1"/>
       <c r="AK596" s="1"/>
     </row>
-    <row r="597" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:37" ht="15.95" customHeight="1">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -24578,7 +24584,7 @@
       <c r="AJ597" s="1"/>
       <c r="AK597" s="1"/>
     </row>
-    <row r="598" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:37" ht="15.95" customHeight="1">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -24617,7 +24623,7 @@
       <c r="AJ598" s="1"/>
       <c r="AK598" s="1"/>
     </row>
-    <row r="599" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:37" ht="15.95" customHeight="1">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -24656,7 +24662,7 @@
       <c r="AJ599" s="1"/>
       <c r="AK599" s="1"/>
     </row>
-    <row r="600" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:37" ht="15.95" customHeight="1">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -24695,7 +24701,7 @@
       <c r="AJ600" s="1"/>
       <c r="AK600" s="1"/>
     </row>
-    <row r="601" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:37" ht="15.95" customHeight="1">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -24734,7 +24740,7 @@
       <c r="AJ601" s="1"/>
       <c r="AK601" s="1"/>
     </row>
-    <row r="602" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:37" ht="15.95" customHeight="1">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -24773,7 +24779,7 @@
       <c r="AJ602" s="1"/>
       <c r="AK602" s="1"/>
     </row>
-    <row r="603" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:37" ht="15.95" customHeight="1">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -24812,7 +24818,7 @@
       <c r="AJ603" s="1"/>
       <c r="AK603" s="1"/>
     </row>
-    <row r="604" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:37" ht="15.95" customHeight="1">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -24851,7 +24857,7 @@
       <c r="AJ604" s="1"/>
       <c r="AK604" s="1"/>
     </row>
-    <row r="605" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:37" ht="15.95" customHeight="1">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -24890,7 +24896,7 @@
       <c r="AJ605" s="1"/>
       <c r="AK605" s="1"/>
     </row>
-    <row r="606" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:37" ht="15.95" customHeight="1">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -24929,7 +24935,7 @@
       <c r="AJ606" s="1"/>
       <c r="AK606" s="1"/>
     </row>
-    <row r="607" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:37" ht="15.95" customHeight="1">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -24968,7 +24974,7 @@
       <c r="AJ607" s="1"/>
       <c r="AK607" s="1"/>
     </row>
-    <row r="608" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:37" ht="15.95" customHeight="1">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -25007,7 +25013,7 @@
       <c r="AJ608" s="1"/>
       <c r="AK608" s="1"/>
     </row>
-    <row r="609" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:37" ht="15.95" customHeight="1">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -25046,7 +25052,7 @@
       <c r="AJ609" s="1"/>
       <c r="AK609" s="1"/>
     </row>
-    <row r="610" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:37" ht="15.95" customHeight="1">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -25085,7 +25091,7 @@
       <c r="AJ610" s="1"/>
       <c r="AK610" s="1"/>
     </row>
-    <row r="611" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:37" ht="15.95" customHeight="1">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -25124,7 +25130,7 @@
       <c r="AJ611" s="1"/>
       <c r="AK611" s="1"/>
     </row>
-    <row r="612" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:37" ht="15.95" customHeight="1">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -25163,7 +25169,7 @@
       <c r="AJ612" s="1"/>
       <c r="AK612" s="1"/>
     </row>
-    <row r="613" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:37" ht="15.95" customHeight="1">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -25202,7 +25208,7 @@
       <c r="AJ613" s="1"/>
       <c r="AK613" s="1"/>
     </row>
-    <row r="614" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:37" ht="15.95" customHeight="1">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -25241,7 +25247,7 @@
       <c r="AJ614" s="1"/>
       <c r="AK614" s="1"/>
     </row>
-    <row r="615" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:37" ht="15.95" customHeight="1">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -25280,7 +25286,7 @@
       <c r="AJ615" s="1"/>
       <c r="AK615" s="1"/>
     </row>
-    <row r="616" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:37" ht="15.95" customHeight="1">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -25319,7 +25325,7 @@
       <c r="AJ616" s="1"/>
       <c r="AK616" s="1"/>
     </row>
-    <row r="617" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:37" ht="15.95" customHeight="1">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -25358,7 +25364,7 @@
       <c r="AJ617" s="1"/>
       <c r="AK617" s="1"/>
     </row>
-    <row r="618" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:37" ht="15.95" customHeight="1">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -25397,7 +25403,7 @@
       <c r="AJ618" s="1"/>
       <c r="AK618" s="1"/>
     </row>
-    <row r="619" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:37" ht="15.95" customHeight="1">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -25436,7 +25442,7 @@
       <c r="AJ619" s="1"/>
       <c r="AK619" s="1"/>
     </row>
-    <row r="620" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:37" ht="15.95" customHeight="1">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -25475,7 +25481,7 @@
       <c r="AJ620" s="1"/>
       <c r="AK620" s="1"/>
     </row>
-    <row r="621" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:37" ht="15.95" customHeight="1">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -25514,7 +25520,7 @@
       <c r="AJ621" s="1"/>
       <c r="AK621" s="1"/>
     </row>
-    <row r="622" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:37" ht="15.95" customHeight="1">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -25553,7 +25559,7 @@
       <c r="AJ622" s="1"/>
       <c r="AK622" s="1"/>
     </row>
-    <row r="623" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:37" ht="15.95" customHeight="1">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -25592,7 +25598,7 @@
       <c r="AJ623" s="1"/>
       <c r="AK623" s="1"/>
     </row>
-    <row r="624" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:37" ht="15.95" customHeight="1">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -25631,7 +25637,7 @@
       <c r="AJ624" s="1"/>
       <c r="AK624" s="1"/>
     </row>
-    <row r="625" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:37" ht="15.95" customHeight="1">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -25670,7 +25676,7 @@
       <c r="AJ625" s="1"/>
       <c r="AK625" s="1"/>
     </row>
-    <row r="626" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:37" ht="15.95" customHeight="1">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -25709,7 +25715,7 @@
       <c r="AJ626" s="1"/>
       <c r="AK626" s="1"/>
     </row>
-    <row r="627" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:37" ht="15.95" customHeight="1">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -25748,7 +25754,7 @@
       <c r="AJ627" s="1"/>
       <c r="AK627" s="1"/>
     </row>
-    <row r="628" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:37" ht="15.95" customHeight="1">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -25787,7 +25793,7 @@
       <c r="AJ628" s="1"/>
       <c r="AK628" s="1"/>
     </row>
-    <row r="629" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:37" ht="15.95" customHeight="1">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -25826,7 +25832,7 @@
       <c r="AJ629" s="1"/>
       <c r="AK629" s="1"/>
     </row>
-    <row r="630" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:37" ht="15.95" customHeight="1">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -25865,7 +25871,7 @@
       <c r="AJ630" s="1"/>
       <c r="AK630" s="1"/>
     </row>
-    <row r="631" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:37" ht="15.95" customHeight="1">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -25904,7 +25910,7 @@
       <c r="AJ631" s="1"/>
       <c r="AK631" s="1"/>
     </row>
-    <row r="632" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:37" ht="15.95" customHeight="1">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -25943,7 +25949,7 @@
       <c r="AJ632" s="1"/>
       <c r="AK632" s="1"/>
     </row>
-    <row r="633" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:37" ht="15.95" customHeight="1">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -25982,7 +25988,7 @@
       <c r="AJ633" s="1"/>
       <c r="AK633" s="1"/>
     </row>
-    <row r="634" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:37" ht="15.95" customHeight="1">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -26021,7 +26027,7 @@
       <c r="AJ634" s="1"/>
       <c r="AK634" s="1"/>
     </row>
-    <row r="635" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:37" ht="15.95" customHeight="1">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -26060,7 +26066,7 @@
       <c r="AJ635" s="1"/>
       <c r="AK635" s="1"/>
     </row>
-    <row r="636" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:37" ht="15.95" customHeight="1">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -26099,7 +26105,7 @@
       <c r="AJ636" s="1"/>
       <c r="AK636" s="1"/>
     </row>
-    <row r="637" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:37" ht="15.95" customHeight="1">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -26138,7 +26144,7 @@
       <c r="AJ637" s="1"/>
       <c r="AK637" s="1"/>
     </row>
-    <row r="638" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:37" ht="15.95" customHeight="1">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -26177,7 +26183,7 @@
       <c r="AJ638" s="1"/>
       <c r="AK638" s="1"/>
     </row>
-    <row r="639" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:37" ht="15.95" customHeight="1">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -26216,7 +26222,7 @@
       <c r="AJ639" s="1"/>
       <c r="AK639" s="1"/>
     </row>
-    <row r="640" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:37" ht="15.95" customHeight="1">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -26255,7 +26261,7 @@
       <c r="AJ640" s="1"/>
       <c r="AK640" s="1"/>
     </row>
-    <row r="641" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:37" ht="15.95" customHeight="1">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -26294,7 +26300,7 @@
       <c r="AJ641" s="1"/>
       <c r="AK641" s="1"/>
     </row>
-    <row r="642" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:37" ht="15.95" customHeight="1">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -26333,7 +26339,7 @@
       <c r="AJ642" s="1"/>
       <c r="AK642" s="1"/>
     </row>
-    <row r="643" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:37" ht="15.95" customHeight="1">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -26372,7 +26378,7 @@
       <c r="AJ643" s="1"/>
       <c r="AK643" s="1"/>
     </row>
-    <row r="644" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:37" ht="15.95" customHeight="1">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -26411,7 +26417,7 @@
       <c r="AJ644" s="1"/>
       <c r="AK644" s="1"/>
     </row>
-    <row r="645" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:37" ht="15.95" customHeight="1">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -26450,7 +26456,7 @@
       <c r="AJ645" s="1"/>
       <c r="AK645" s="1"/>
     </row>
-    <row r="646" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:37" ht="15.95" customHeight="1">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -26489,7 +26495,7 @@
       <c r="AJ646" s="1"/>
       <c r="AK646" s="1"/>
     </row>
-    <row r="647" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:37" ht="15.95" customHeight="1">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -26528,7 +26534,7 @@
       <c r="AJ647" s="1"/>
       <c r="AK647" s="1"/>
     </row>
-    <row r="648" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:37" ht="15.95" customHeight="1">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -26567,7 +26573,7 @@
       <c r="AJ648" s="1"/>
       <c r="AK648" s="1"/>
     </row>
-    <row r="649" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:37" ht="15.95" customHeight="1">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -26606,7 +26612,7 @@
       <c r="AJ649" s="1"/>
       <c r="AK649" s="1"/>
     </row>
-    <row r="650" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:37" ht="15.95" customHeight="1">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -26645,7 +26651,7 @@
       <c r="AJ650" s="1"/>
       <c r="AK650" s="1"/>
     </row>
-    <row r="651" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:37" ht="15.95" customHeight="1">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -26684,7 +26690,7 @@
       <c r="AJ651" s="1"/>
       <c r="AK651" s="1"/>
     </row>
-    <row r="652" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:37" ht="15.95" customHeight="1">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -26723,7 +26729,7 @@
       <c r="AJ652" s="1"/>
       <c r="AK652" s="1"/>
     </row>
-    <row r="653" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:37" ht="15.95" customHeight="1">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -26762,7 +26768,7 @@
       <c r="AJ653" s="1"/>
       <c r="AK653" s="1"/>
     </row>
-    <row r="654" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:37" ht="15.95" customHeight="1">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -26801,7 +26807,7 @@
       <c r="AJ654" s="1"/>
       <c r="AK654" s="1"/>
     </row>
-    <row r="655" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:37" ht="15.95" customHeight="1">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -26840,7 +26846,7 @@
       <c r="AJ655" s="1"/>
       <c r="AK655" s="1"/>
     </row>
-    <row r="656" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:37" ht="15.95" customHeight="1">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -26879,7 +26885,7 @@
       <c r="AJ656" s="1"/>
       <c r="AK656" s="1"/>
     </row>
-    <row r="657" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:37" ht="15.95" customHeight="1">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -26918,7 +26924,7 @@
       <c r="AJ657" s="1"/>
       <c r="AK657" s="1"/>
     </row>
-    <row r="658" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:37" ht="15.95" customHeight="1">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -26957,7 +26963,7 @@
       <c r="AJ658" s="1"/>
       <c r="AK658" s="1"/>
     </row>
-    <row r="659" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:37" ht="15.95" customHeight="1">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -26996,7 +27002,7 @@
       <c r="AJ659" s="1"/>
       <c r="AK659" s="1"/>
     </row>
-    <row r="660" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:37" ht="15.95" customHeight="1">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -27035,7 +27041,7 @@
       <c r="AJ660" s="1"/>
       <c r="AK660" s="1"/>
     </row>
-    <row r="661" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:37" ht="15.95" customHeight="1">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -27074,7 +27080,7 @@
       <c r="AJ661" s="1"/>
       <c r="AK661" s="1"/>
     </row>
-    <row r="662" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:37" ht="15.95" customHeight="1">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -27113,7 +27119,7 @@
       <c r="AJ662" s="1"/>
       <c r="AK662" s="1"/>
     </row>
-    <row r="663" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:37" ht="15.95" customHeight="1">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -27152,7 +27158,7 @@
       <c r="AJ663" s="1"/>
       <c r="AK663" s="1"/>
     </row>
-    <row r="664" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:37" ht="15.95" customHeight="1">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -27191,7 +27197,7 @@
       <c r="AJ664" s="1"/>
       <c r="AK664" s="1"/>
     </row>
-    <row r="665" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:37" ht="15.95" customHeight="1">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -27230,7 +27236,7 @@
       <c r="AJ665" s="1"/>
       <c r="AK665" s="1"/>
     </row>
-    <row r="666" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:37" ht="15.95" customHeight="1">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -27269,7 +27275,7 @@
       <c r="AJ666" s="1"/>
       <c r="AK666" s="1"/>
     </row>
-    <row r="667" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:37" ht="15.95" customHeight="1">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -27308,7 +27314,7 @@
       <c r="AJ667" s="1"/>
       <c r="AK667" s="1"/>
     </row>
-    <row r="668" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:37" ht="15.95" customHeight="1">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -27347,7 +27353,7 @@
       <c r="AJ668" s="1"/>
       <c r="AK668" s="1"/>
     </row>
-    <row r="669" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:37" ht="15.95" customHeight="1">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -27386,7 +27392,7 @@
       <c r="AJ669" s="1"/>
       <c r="AK669" s="1"/>
     </row>
-    <row r="670" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:37" ht="15.95" customHeight="1">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -27425,7 +27431,7 @@
       <c r="AJ670" s="1"/>
       <c r="AK670" s="1"/>
     </row>
-    <row r="671" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:37" ht="15.95" customHeight="1">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -27464,7 +27470,7 @@
       <c r="AJ671" s="1"/>
       <c r="AK671" s="1"/>
     </row>
-    <row r="672" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:37" ht="15.95" customHeight="1">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -27503,7 +27509,7 @@
       <c r="AJ672" s="1"/>
       <c r="AK672" s="1"/>
     </row>
-    <row r="673" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:37" ht="15.95" customHeight="1">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -27542,7 +27548,7 @@
       <c r="AJ673" s="1"/>
       <c r="AK673" s="1"/>
     </row>
-    <row r="674" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:37" ht="15.95" customHeight="1">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -27581,7 +27587,7 @@
       <c r="AJ674" s="1"/>
       <c r="AK674" s="1"/>
     </row>
-    <row r="675" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:37" ht="15.95" customHeight="1">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -27620,7 +27626,7 @@
       <c r="AJ675" s="1"/>
       <c r="AK675" s="1"/>
     </row>
-    <row r="676" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:37" ht="15.95" customHeight="1">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -27659,7 +27665,7 @@
       <c r="AJ676" s="1"/>
       <c r="AK676" s="1"/>
     </row>
-    <row r="677" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:37" ht="15.95" customHeight="1">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -27698,7 +27704,7 @@
       <c r="AJ677" s="1"/>
       <c r="AK677" s="1"/>
     </row>
-    <row r="678" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:37" ht="15.95" customHeight="1">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -27737,7 +27743,7 @@
       <c r="AJ678" s="1"/>
       <c r="AK678" s="1"/>
     </row>
-    <row r="679" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:37" ht="15.95" customHeight="1">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -27776,7 +27782,7 @@
       <c r="AJ679" s="1"/>
       <c r="AK679" s="1"/>
     </row>
-    <row r="680" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:37" ht="15.95" customHeight="1">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -27815,7 +27821,7 @@
       <c r="AJ680" s="1"/>
       <c r="AK680" s="1"/>
     </row>
-    <row r="681" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:37" ht="15.95" customHeight="1">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -27854,7 +27860,7 @@
       <c r="AJ681" s="1"/>
       <c r="AK681" s="1"/>
     </row>
-    <row r="682" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:37" ht="15.95" customHeight="1">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -27893,7 +27899,7 @@
       <c r="AJ682" s="1"/>
       <c r="AK682" s="1"/>
     </row>
-    <row r="683" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:37" ht="15.95" customHeight="1">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -27932,7 +27938,7 @@
       <c r="AJ683" s="1"/>
       <c r="AK683" s="1"/>
     </row>
-    <row r="684" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:37" ht="15.95" customHeight="1">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -27971,7 +27977,7 @@
       <c r="AJ684" s="1"/>
       <c r="AK684" s="1"/>
     </row>
-    <row r="685" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:37" ht="15.95" customHeight="1">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -28010,7 +28016,7 @@
       <c r="AJ685" s="1"/>
       <c r="AK685" s="1"/>
     </row>
-    <row r="686" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:37" ht="15.95" customHeight="1">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -28049,7 +28055,7 @@
       <c r="AJ686" s="1"/>
       <c r="AK686" s="1"/>
     </row>
-    <row r="687" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:37" ht="15.95" customHeight="1">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -28088,7 +28094,7 @@
       <c r="AJ687" s="1"/>
       <c r="AK687" s="1"/>
     </row>
-    <row r="688" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:37" ht="15.95" customHeight="1">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -28127,7 +28133,7 @@
       <c r="AJ688" s="1"/>
       <c r="AK688" s="1"/>
     </row>
-    <row r="689" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:37" ht="15.95" customHeight="1">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -28166,7 +28172,7 @@
       <c r="AJ689" s="1"/>
       <c r="AK689" s="1"/>
     </row>
-    <row r="690" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:37" ht="15.95" customHeight="1">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -28205,7 +28211,7 @@
       <c r="AJ690" s="1"/>
       <c r="AK690" s="1"/>
     </row>
-    <row r="691" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:37" ht="15.95" customHeight="1">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -28244,7 +28250,7 @@
       <c r="AJ691" s="1"/>
       <c r="AK691" s="1"/>
     </row>
-    <row r="692" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:37" ht="15.95" customHeight="1">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -28283,7 +28289,7 @@
       <c r="AJ692" s="1"/>
       <c r="AK692" s="1"/>
     </row>
-    <row r="693" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:37" ht="15.95" customHeight="1">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -28322,7 +28328,7 @@
       <c r="AJ693" s="1"/>
       <c r="AK693" s="1"/>
     </row>
-    <row r="694" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:37" ht="15.95" customHeight="1">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -28361,7 +28367,7 @@
       <c r="AJ694" s="1"/>
       <c r="AK694" s="1"/>
     </row>
-    <row r="695" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:37" ht="15.95" customHeight="1">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -28400,7 +28406,7 @@
       <c r="AJ695" s="1"/>
       <c r="AK695" s="1"/>
     </row>
-    <row r="696" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:37" ht="15.95" customHeight="1">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -28439,7 +28445,7 @@
       <c r="AJ696" s="1"/>
       <c r="AK696" s="1"/>
     </row>
-    <row r="697" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:37" ht="15.95" customHeight="1">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -28478,7 +28484,7 @@
       <c r="AJ697" s="1"/>
       <c r="AK697" s="1"/>
     </row>
-    <row r="698" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:37" ht="15.95" customHeight="1">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -28517,7 +28523,7 @@
       <c r="AJ698" s="1"/>
       <c r="AK698" s="1"/>
     </row>
-    <row r="699" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:37" ht="15.95" customHeight="1">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -28556,7 +28562,7 @@
       <c r="AJ699" s="1"/>
       <c r="AK699" s="1"/>
     </row>
-    <row r="700" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:37" ht="15.95" customHeight="1">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -28595,7 +28601,7 @@
       <c r="AJ700" s="1"/>
       <c r="AK700" s="1"/>
     </row>
-    <row r="701" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:37" ht="15.95" customHeight="1">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -28634,7 +28640,7 @@
       <c r="AJ701" s="1"/>
       <c r="AK701" s="1"/>
     </row>
-    <row r="702" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:37" ht="15.95" customHeight="1">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -28673,7 +28679,7 @@
       <c r="AJ702" s="1"/>
       <c r="AK702" s="1"/>
     </row>
-    <row r="703" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:37" ht="15.95" customHeight="1">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -28712,7 +28718,7 @@
       <c r="AJ703" s="1"/>
       <c r="AK703" s="1"/>
     </row>
-    <row r="704" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:37" ht="15.95" customHeight="1">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -28751,7 +28757,7 @@
       <c r="AJ704" s="1"/>
       <c r="AK704" s="1"/>
     </row>
-    <row r="705" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:37" ht="15.95" customHeight="1">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -28790,7 +28796,7 @@
       <c r="AJ705" s="1"/>
       <c r="AK705" s="1"/>
     </row>
-    <row r="706" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:37" ht="15.95" customHeight="1">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -28829,7 +28835,7 @@
       <c r="AJ706" s="1"/>
       <c r="AK706" s="1"/>
     </row>
-    <row r="707" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:37" ht="15.95" customHeight="1">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -28868,7 +28874,7 @@
       <c r="AJ707" s="1"/>
       <c r="AK707" s="1"/>
     </row>
-    <row r="708" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:37" ht="15.95" customHeight="1">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -28907,7 +28913,7 @@
       <c r="AJ708" s="1"/>
       <c r="AK708" s="1"/>
     </row>
-    <row r="709" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:37" ht="15.95" customHeight="1">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -28946,7 +28952,7 @@
       <c r="AJ709" s="1"/>
       <c r="AK709" s="1"/>
     </row>
-    <row r="710" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:37" ht="15.95" customHeight="1">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -28985,7 +28991,7 @@
       <c r="AJ710" s="1"/>
       <c r="AK710" s="1"/>
     </row>
-    <row r="711" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:37" ht="15.95" customHeight="1">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -29024,7 +29030,7 @@
       <c r="AJ711" s="1"/>
       <c r="AK711" s="1"/>
     </row>
-    <row r="712" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:37" ht="15.95" customHeight="1">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -29063,7 +29069,7 @@
       <c r="AJ712" s="1"/>
       <c r="AK712" s="1"/>
     </row>
-    <row r="713" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:37" ht="15.95" customHeight="1">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -29102,7 +29108,7 @@
       <c r="AJ713" s="1"/>
       <c r="AK713" s="1"/>
     </row>
-    <row r="714" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:37" ht="15.95" customHeight="1">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -29141,7 +29147,7 @@
       <c r="AJ714" s="1"/>
       <c r="AK714" s="1"/>
     </row>
-    <row r="715" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:37" ht="15.95" customHeight="1">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -29180,7 +29186,7 @@
       <c r="AJ715" s="1"/>
       <c r="AK715" s="1"/>
     </row>
-    <row r="716" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:37" ht="15.95" customHeight="1">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -29219,7 +29225,7 @@
       <c r="AJ716" s="1"/>
       <c r="AK716" s="1"/>
     </row>
-    <row r="717" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:37" ht="15.95" customHeight="1">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -29258,7 +29264,7 @@
       <c r="AJ717" s="1"/>
       <c r="AK717" s="1"/>
     </row>
-    <row r="718" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:37" ht="15.95" customHeight="1">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -29297,7 +29303,7 @@
       <c r="AJ718" s="1"/>
       <c r="AK718" s="1"/>
     </row>
-    <row r="719" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:37" ht="15.95" customHeight="1">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -29336,7 +29342,7 @@
       <c r="AJ719" s="1"/>
       <c r="AK719" s="1"/>
     </row>
-    <row r="720" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:37" ht="15.95" customHeight="1">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -29375,7 +29381,7 @@
       <c r="AJ720" s="1"/>
       <c r="AK720" s="1"/>
     </row>
-    <row r="721" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:37" ht="15.95" customHeight="1">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -29414,7 +29420,7 @@
       <c r="AJ721" s="1"/>
       <c r="AK721" s="1"/>
     </row>
-    <row r="722" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:37" ht="15.95" customHeight="1">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -29453,7 +29459,7 @@
       <c r="AJ722" s="1"/>
       <c r="AK722" s="1"/>
     </row>
-    <row r="723" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:37" ht="15.95" customHeight="1">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -29492,7 +29498,7 @@
       <c r="AJ723" s="1"/>
       <c r="AK723" s="1"/>
     </row>
-    <row r="724" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:37" ht="15.95" customHeight="1">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -29531,7 +29537,7 @@
       <c r="AJ724" s="1"/>
       <c r="AK724" s="1"/>
     </row>
-    <row r="725" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:37" ht="15.95" customHeight="1">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -29570,7 +29576,7 @@
       <c r="AJ725" s="1"/>
       <c r="AK725" s="1"/>
     </row>
-    <row r="726" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:37" ht="15.95" customHeight="1">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -29609,7 +29615,7 @@
       <c r="AJ726" s="1"/>
       <c r="AK726" s="1"/>
     </row>
-    <row r="727" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:37" ht="15.95" customHeight="1">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -29648,7 +29654,7 @@
       <c r="AJ727" s="1"/>
       <c r="AK727" s="1"/>
     </row>
-    <row r="728" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:37" ht="15.95" customHeight="1">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -29687,7 +29693,7 @@
       <c r="AJ728" s="1"/>
       <c r="AK728" s="1"/>
     </row>
-    <row r="729" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:37" ht="15.95" customHeight="1">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -29726,7 +29732,7 @@
       <c r="AJ729" s="1"/>
       <c r="AK729" s="1"/>
     </row>
-    <row r="730" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:37" ht="15.95" customHeight="1">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -29765,7 +29771,7 @@
       <c r="AJ730" s="1"/>
       <c r="AK730" s="1"/>
     </row>
-    <row r="731" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:37" ht="15.95" customHeight="1">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -29804,7 +29810,7 @@
       <c r="AJ731" s="1"/>
       <c r="AK731" s="1"/>
     </row>
-    <row r="732" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:37" ht="15.95" customHeight="1">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -29843,7 +29849,7 @@
       <c r="AJ732" s="1"/>
       <c r="AK732" s="1"/>
     </row>
-    <row r="733" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:37" ht="15.95" customHeight="1">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -29882,7 +29888,7 @@
       <c r="AJ733" s="1"/>
       <c r="AK733" s="1"/>
     </row>
-    <row r="734" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:37" ht="15.95" customHeight="1">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -29921,7 +29927,7 @@
       <c r="AJ734" s="1"/>
       <c r="AK734" s="1"/>
     </row>
-    <row r="735" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:37" ht="15.95" customHeight="1">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -29960,7 +29966,7 @@
       <c r="AJ735" s="1"/>
       <c r="AK735" s="1"/>
     </row>
-    <row r="736" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:37" ht="15.95" customHeight="1">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -29999,7 +30005,7 @@
       <c r="AJ736" s="1"/>
       <c r="AK736" s="1"/>
     </row>
-    <row r="737" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:37" ht="15.95" customHeight="1">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -30038,7 +30044,7 @@
       <c r="AJ737" s="1"/>
       <c r="AK737" s="1"/>
     </row>
-    <row r="738" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:37" ht="15.95" customHeight="1">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -30077,7 +30083,7 @@
       <c r="AJ738" s="1"/>
       <c r="AK738" s="1"/>
     </row>
-    <row r="739" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:37" ht="15.95" customHeight="1">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -30116,7 +30122,7 @@
       <c r="AJ739" s="1"/>
       <c r="AK739" s="1"/>
     </row>
-    <row r="740" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:37" ht="15.95" customHeight="1">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -30155,7 +30161,7 @@
       <c r="AJ740" s="1"/>
       <c r="AK740" s="1"/>
     </row>
-    <row r="741" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:37" ht="15.95" customHeight="1">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -30194,7 +30200,7 @@
       <c r="AJ741" s="1"/>
       <c r="AK741" s="1"/>
     </row>
-    <row r="742" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:37" ht="15.95" customHeight="1">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -30233,7 +30239,7 @@
       <c r="AJ742" s="1"/>
       <c r="AK742" s="1"/>
     </row>
-    <row r="743" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:37" ht="15.95" customHeight="1">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -30272,7 +30278,7 @@
       <c r="AJ743" s="1"/>
       <c r="AK743" s="1"/>
     </row>
-    <row r="744" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:37" ht="15.95" customHeight="1">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -30311,7 +30317,7 @@
       <c r="AJ744" s="1"/>
       <c r="AK744" s="1"/>
     </row>
-    <row r="745" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:37" ht="15.95" customHeight="1">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -30350,7 +30356,7 @@
       <c r="AJ745" s="1"/>
       <c r="AK745" s="1"/>
     </row>
-    <row r="746" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:37" ht="15.95" customHeight="1">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -30389,7 +30395,7 @@
       <c r="AJ746" s="1"/>
       <c r="AK746" s="1"/>
     </row>
-    <row r="747" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:37" ht="15.95" customHeight="1">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -30428,7 +30434,7 @@
       <c r="AJ747" s="1"/>
       <c r="AK747" s="1"/>
     </row>
-    <row r="748" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:37" ht="15.95" customHeight="1">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -30467,7 +30473,7 @@
       <c r="AJ748" s="1"/>
       <c r="AK748" s="1"/>
     </row>
-    <row r="749" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:37" ht="15.95" customHeight="1">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -30506,7 +30512,7 @@
       <c r="AJ749" s="1"/>
       <c r="AK749" s="1"/>
     </row>
-    <row r="750" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:37" ht="15.95" customHeight="1">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -30545,7 +30551,7 @@
       <c r="AJ750" s="1"/>
       <c r="AK750" s="1"/>
     </row>
-    <row r="751" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:37" ht="15.95" customHeight="1">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -30584,7 +30590,7 @@
       <c r="AJ751" s="1"/>
       <c r="AK751" s="1"/>
     </row>
-    <row r="752" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:37" ht="15.95" customHeight="1">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -30623,7 +30629,7 @@
       <c r="AJ752" s="1"/>
       <c r="AK752" s="1"/>
     </row>
-    <row r="753" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:37" ht="15.95" customHeight="1">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -30662,7 +30668,7 @@
       <c r="AJ753" s="1"/>
       <c r="AK753" s="1"/>
     </row>
-    <row r="754" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:37" ht="15.95" customHeight="1">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -30701,7 +30707,7 @@
       <c r="AJ754" s="1"/>
       <c r="AK754" s="1"/>
     </row>
-    <row r="755" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:37" ht="15.95" customHeight="1">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -30740,7 +30746,7 @@
       <c r="AJ755" s="1"/>
       <c r="AK755" s="1"/>
     </row>
-    <row r="756" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:37" ht="15.95" customHeight="1">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -30779,7 +30785,7 @@
       <c r="AJ756" s="1"/>
       <c r="AK756" s="1"/>
     </row>
-    <row r="757" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:37" ht="15.95" customHeight="1">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -30818,7 +30824,7 @@
       <c r="AJ757" s="1"/>
       <c r="AK757" s="1"/>
     </row>
-    <row r="758" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:37" ht="15.95" customHeight="1">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -30857,7 +30863,7 @@
       <c r="AJ758" s="1"/>
       <c r="AK758" s="1"/>
     </row>
-    <row r="759" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:37" ht="15.95" customHeight="1">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -30896,7 +30902,7 @@
       <c r="AJ759" s="1"/>
       <c r="AK759" s="1"/>
     </row>
-    <row r="760" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:37" ht="15.95" customHeight="1">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -30935,7 +30941,7 @@
       <c r="AJ760" s="1"/>
       <c r="AK760" s="1"/>
     </row>
-    <row r="761" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:37" ht="15.95" customHeight="1">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -30974,7 +30980,7 @@
       <c r="AJ761" s="1"/>
       <c r="AK761" s="1"/>
     </row>
-    <row r="762" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:37" ht="15.95" customHeight="1">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -31013,7 +31019,7 @@
       <c r="AJ762" s="1"/>
       <c r="AK762" s="1"/>
     </row>
-    <row r="763" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:37" ht="15.95" customHeight="1">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -31052,7 +31058,7 @@
       <c r="AJ763" s="1"/>
       <c r="AK763" s="1"/>
     </row>
-    <row r="764" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:37" ht="15.95" customHeight="1">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -31091,7 +31097,7 @@
       <c r="AJ764" s="1"/>
       <c r="AK764" s="1"/>
     </row>
-    <row r="765" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:37" ht="15.95" customHeight="1">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -31130,7 +31136,7 @@
       <c r="AJ765" s="1"/>
       <c r="AK765" s="1"/>
     </row>
-    <row r="766" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:37" ht="15.95" customHeight="1">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -31169,7 +31175,7 @@
       <c r="AJ766" s="1"/>
       <c r="AK766" s="1"/>
     </row>
-    <row r="767" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:37" ht="15.95" customHeight="1">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -31208,7 +31214,7 @@
       <c r="AJ767" s="1"/>
       <c r="AK767" s="1"/>
     </row>
-    <row r="768" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:37" ht="15.95" customHeight="1">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -31247,7 +31253,7 @@
       <c r="AJ768" s="1"/>
       <c r="AK768" s="1"/>
     </row>
-    <row r="769" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:37" ht="15.95" customHeight="1">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -31286,7 +31292,7 @@
       <c r="AJ769" s="1"/>
       <c r="AK769" s="1"/>
     </row>
-    <row r="770" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:37" ht="15.95" customHeight="1">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -31325,7 +31331,7 @@
       <c r="AJ770" s="1"/>
       <c r="AK770" s="1"/>
     </row>
-    <row r="771" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:37" ht="15.95" customHeight="1">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -31364,7 +31370,7 @@
       <c r="AJ771" s="1"/>
       <c r="AK771" s="1"/>
     </row>
-    <row r="772" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:37" ht="15.95" customHeight="1">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -31403,7 +31409,7 @@
       <c r="AJ772" s="1"/>
       <c r="AK772" s="1"/>
     </row>
-    <row r="773" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:37" ht="15.95" customHeight="1">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -31442,7 +31448,7 @@
       <c r="AJ773" s="1"/>
       <c r="AK773" s="1"/>
     </row>
-    <row r="774" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:37" ht="15.95" customHeight="1">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -31481,7 +31487,7 @@
       <c r="AJ774" s="1"/>
       <c r="AK774" s="1"/>
     </row>
-    <row r="775" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:37" ht="15.95" customHeight="1">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -31520,7 +31526,7 @@
       <c r="AJ775" s="1"/>
       <c r="AK775" s="1"/>
     </row>
-    <row r="776" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:37" ht="15.95" customHeight="1">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -31559,7 +31565,7 @@
       <c r="AJ776" s="1"/>
       <c r="AK776" s="1"/>
     </row>
-    <row r="777" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:37" ht="15.95" customHeight="1">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -31598,7 +31604,7 @@
       <c r="AJ777" s="1"/>
       <c r="AK777" s="1"/>
     </row>
-    <row r="778" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:37" ht="15.95" customHeight="1">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -31637,7 +31643,7 @@
       <c r="AJ778" s="1"/>
       <c r="AK778" s="1"/>
     </row>
-    <row r="779" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:37" ht="15.95" customHeight="1">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -31676,7 +31682,7 @@
       <c r="AJ779" s="1"/>
       <c r="AK779" s="1"/>
     </row>
-    <row r="780" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:37" ht="15.95" customHeight="1">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -31715,7 +31721,7 @@
       <c r="AJ780" s="1"/>
       <c r="AK780" s="1"/>
     </row>
-    <row r="781" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:37" ht="15.95" customHeight="1">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -31754,7 +31760,7 @@
       <c r="AJ781" s="1"/>
       <c r="AK781" s="1"/>
     </row>
-    <row r="782" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:37" ht="15.95" customHeight="1">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -31793,7 +31799,7 @@
       <c r="AJ782" s="1"/>
       <c r="AK782" s="1"/>
     </row>
-    <row r="783" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:37" ht="15.95" customHeight="1">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -31832,7 +31838,7 @@
       <c r="AJ783" s="1"/>
       <c r="AK783" s="1"/>
     </row>
-    <row r="784" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:37" ht="15.95" customHeight="1">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -31871,7 +31877,7 @@
       <c r="AJ784" s="1"/>
       <c r="AK784" s="1"/>
     </row>
-    <row r="785" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:37" ht="15.95" customHeight="1">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -31910,7 +31916,7 @@
       <c r="AJ785" s="1"/>
       <c r="AK785" s="1"/>
     </row>
-    <row r="786" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:37" ht="15.95" customHeight="1">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -31949,7 +31955,7 @@
       <c r="AJ786" s="1"/>
       <c r="AK786" s="1"/>
     </row>
-    <row r="787" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:37" ht="15.95" customHeight="1">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -31988,7 +31994,7 @@
       <c r="AJ787" s="1"/>
       <c r="AK787" s="1"/>
     </row>
-    <row r="788" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:37" ht="15.95" customHeight="1">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -32027,7 +32033,7 @@
       <c r="AJ788" s="1"/>
       <c r="AK788" s="1"/>
     </row>
-    <row r="789" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:37" ht="15.95" customHeight="1">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -32066,7 +32072,7 @@
       <c r="AJ789" s="1"/>
       <c r="AK789" s="1"/>
     </row>
-    <row r="790" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:37" ht="15.95" customHeight="1">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -32105,7 +32111,7 @@
       <c r="AJ790" s="1"/>
       <c r="AK790" s="1"/>
     </row>
-    <row r="791" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:37" ht="15.95" customHeight="1">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -32144,7 +32150,7 @@
       <c r="AJ791" s="1"/>
       <c r="AK791" s="1"/>
     </row>
-    <row r="792" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:37" ht="15.95" customHeight="1">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -32183,7 +32189,7 @@
       <c r="AJ792" s="1"/>
       <c r="AK792" s="1"/>
     </row>
-    <row r="793" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:37" ht="15.95" customHeight="1">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -32222,7 +32228,7 @@
       <c r="AJ793" s="1"/>
       <c r="AK793" s="1"/>
     </row>
-    <row r="794" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:37" ht="15.95" customHeight="1">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -32261,7 +32267,7 @@
       <c r="AJ794" s="1"/>
       <c r="AK794" s="1"/>
     </row>
-    <row r="795" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:37" ht="15.95" customHeight="1">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -32300,7 +32306,7 @@
       <c r="AJ795" s="1"/>
       <c r="AK795" s="1"/>
     </row>
-    <row r="796" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:37" ht="15.95" customHeight="1">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -32339,7 +32345,7 @@
       <c r="AJ796" s="1"/>
       <c r="AK796" s="1"/>
     </row>
-    <row r="797" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:37" ht="15.95" customHeight="1">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -32378,7 +32384,7 @@
       <c r="AJ797" s="1"/>
       <c r="AK797" s="1"/>
     </row>
-    <row r="798" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:37" ht="15.95" customHeight="1">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -32417,7 +32423,7 @@
       <c r="AJ798" s="1"/>
       <c r="AK798" s="1"/>
     </row>
-    <row r="799" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:37" ht="15.95" customHeight="1">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -32456,7 +32462,7 @@
       <c r="AJ799" s="1"/>
       <c r="AK799" s="1"/>
     </row>
-    <row r="800" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:37" ht="15.95" customHeight="1">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -32495,7 +32501,7 @@
       <c r="AJ800" s="1"/>
       <c r="AK800" s="1"/>
     </row>
-    <row r="801" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:37" ht="15.95" customHeight="1">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -32534,7 +32540,7 @@
       <c r="AJ801" s="1"/>
       <c r="AK801" s="1"/>
     </row>
-    <row r="802" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:37" ht="15.95" customHeight="1">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -32573,7 +32579,7 @@
       <c r="AJ802" s="1"/>
       <c r="AK802" s="1"/>
     </row>
-    <row r="803" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:37" ht="15.95" customHeight="1">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -32612,7 +32618,7 @@
       <c r="AJ803" s="1"/>
       <c r="AK803" s="1"/>
     </row>
-    <row r="804" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:37" ht="15.95" customHeight="1">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -32651,7 +32657,7 @@
       <c r="AJ804" s="1"/>
       <c r="AK804" s="1"/>
     </row>
-    <row r="805" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:37" ht="15.95" customHeight="1">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -32690,7 +32696,7 @@
       <c r="AJ805" s="1"/>
       <c r="AK805" s="1"/>
     </row>
-    <row r="806" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:37" ht="15.95" customHeight="1">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -32729,7 +32735,7 @@
       <c r="AJ806" s="1"/>
       <c r="AK806" s="1"/>
     </row>
-    <row r="807" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:37" ht="15.95" customHeight="1">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -32768,7 +32774,7 @@
       <c r="AJ807" s="1"/>
       <c r="AK807" s="1"/>
     </row>
-    <row r="808" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:37" ht="15.95" customHeight="1">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -32807,7 +32813,7 @@
       <c r="AJ808" s="1"/>
       <c r="AK808" s="1"/>
     </row>
-    <row r="809" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:37" ht="15.95" customHeight="1">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -32846,7 +32852,7 @@
       <c r="AJ809" s="1"/>
       <c r="AK809" s="1"/>
     </row>
-    <row r="810" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:37" ht="15.95" customHeight="1">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -32885,7 +32891,7 @@
       <c r="AJ810" s="1"/>
       <c r="AK810" s="1"/>
     </row>
-    <row r="811" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:37" ht="15.95" customHeight="1">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -32924,7 +32930,7 @@
       <c r="AJ811" s="1"/>
       <c r="AK811" s="1"/>
     </row>
-    <row r="812" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:37" ht="15.95" customHeight="1">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -32963,7 +32969,7 @@
       <c r="AJ812" s="1"/>
       <c r="AK812" s="1"/>
     </row>
-    <row r="813" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:37" ht="15.95" customHeight="1">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -33002,7 +33008,7 @@
       <c r="AJ813" s="1"/>
       <c r="AK813" s="1"/>
     </row>
-    <row r="814" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:37" ht="15.95" customHeight="1">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -33041,7 +33047,7 @@
       <c r="AJ814" s="1"/>
       <c r="AK814" s="1"/>
     </row>
-    <row r="815" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:37" ht="15.95" customHeight="1">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -33080,7 +33086,7 @@
       <c r="AJ815" s="1"/>
       <c r="AK815" s="1"/>
     </row>
-    <row r="816" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:37" ht="15.95" customHeight="1">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -33119,7 +33125,7 @@
       <c r="AJ816" s="1"/>
       <c r="AK816" s="1"/>
     </row>
-    <row r="817" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:37" ht="15.95" customHeight="1">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -33158,7 +33164,7 @@
       <c r="AJ817" s="1"/>
       <c r="AK817" s="1"/>
     </row>
-    <row r="818" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:37" ht="15.95" customHeight="1">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -33197,7 +33203,7 @@
       <c r="AJ818" s="1"/>
       <c r="AK818" s="1"/>
     </row>
-    <row r="819" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:37" ht="15.95" customHeight="1">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -33236,7 +33242,7 @@
       <c r="AJ819" s="1"/>
       <c r="AK819" s="1"/>
     </row>
-    <row r="820" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:37" ht="15.95" customHeight="1">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -33275,7 +33281,7 @@
       <c r="AJ820" s="1"/>
       <c r="AK820" s="1"/>
     </row>
-    <row r="821" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:37" ht="15.95" customHeight="1">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -33314,7 +33320,7 @@
       <c r="AJ821" s="1"/>
       <c r="AK821" s="1"/>
     </row>
-    <row r="822" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:37" ht="15.95" customHeight="1">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -33353,7 +33359,7 @@
       <c r="AJ822" s="1"/>
       <c r="AK822" s="1"/>
     </row>
-    <row r="823" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:37" ht="15.95" customHeight="1">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -33392,7 +33398,7 @@
       <c r="AJ823" s="1"/>
       <c r="AK823" s="1"/>
     </row>
-    <row r="824" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:37" ht="15.95" customHeight="1">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -33431,7 +33437,7 @@
       <c r="AJ824" s="1"/>
       <c r="AK824" s="1"/>
     </row>
-    <row r="825" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:37" ht="15.95" customHeight="1">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -33470,7 +33476,7 @@
       <c r="AJ825" s="1"/>
       <c r="AK825" s="1"/>
     </row>
-    <row r="826" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:37" ht="15.95" customHeight="1">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -33509,7 +33515,7 @@
       <c r="AJ826" s="1"/>
       <c r="AK826" s="1"/>
     </row>
-    <row r="827" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:37" ht="15.95" customHeight="1">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -33548,7 +33554,7 @@
       <c r="AJ827" s="1"/>
       <c r="AK827" s="1"/>
     </row>
-    <row r="828" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:37" ht="15.95" customHeight="1">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -33587,7 +33593,7 @@
       <c r="AJ828" s="1"/>
       <c r="AK828" s="1"/>
     </row>
-    <row r="829" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:37" ht="15.95" customHeight="1">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -33626,7 +33632,7 @@
       <c r="AJ829" s="1"/>
       <c r="AK829" s="1"/>
     </row>
-    <row r="830" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:37" ht="15.95" customHeight="1">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -33665,7 +33671,7 @@
       <c r="AJ830" s="1"/>
       <c r="AK830" s="1"/>
     </row>
-    <row r="831" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:37" ht="15.95" customHeight="1">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -33704,7 +33710,7 @@
       <c r="AJ831" s="1"/>
       <c r="AK831" s="1"/>
     </row>
-    <row r="832" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:37" ht="15.95" customHeight="1">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -33743,7 +33749,7 @@
       <c r="AJ832" s="1"/>
       <c r="AK832" s="1"/>
     </row>
-    <row r="833" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:37" ht="15.95" customHeight="1">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -33782,7 +33788,7 @@
       <c r="AJ833" s="1"/>
       <c r="AK833" s="1"/>
     </row>
-    <row r="834" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:37" ht="15.95" customHeight="1">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -33821,7 +33827,7 @@
       <c r="AJ834" s="1"/>
       <c r="AK834" s="1"/>
     </row>
-    <row r="835" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:37" ht="15.95" customHeight="1">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -33860,7 +33866,7 @@
       <c r="AJ835" s="1"/>
       <c r="AK835" s="1"/>
     </row>
-    <row r="836" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:37" ht="15.95" customHeight="1">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -33899,7 +33905,7 @@
       <c r="AJ836" s="1"/>
       <c r="AK836" s="1"/>
     </row>
-    <row r="837" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:37" ht="15.95" customHeight="1">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -33938,7 +33944,7 @@
       <c r="AJ837" s="1"/>
       <c r="AK837" s="1"/>
     </row>
-    <row r="838" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:37" ht="15.95" customHeight="1">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -33977,7 +33983,7 @@
       <c r="AJ838" s="1"/>
       <c r="AK838" s="1"/>
     </row>
-    <row r="839" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:37" ht="15.95" customHeight="1">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -34016,7 +34022,7 @@
       <c r="AJ839" s="1"/>
       <c r="AK839" s="1"/>
     </row>
-    <row r="840" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:37" ht="15.95" customHeight="1">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -34055,7 +34061,7 @@
       <c r="AJ840" s="1"/>
       <c r="AK840" s="1"/>
     </row>
-    <row r="841" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:37" ht="15.95" customHeight="1">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -34094,7 +34100,7 @@
       <c r="AJ841" s="1"/>
       <c r="AK841" s="1"/>
     </row>
-    <row r="842" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:37" ht="15.95" customHeight="1">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -34133,7 +34139,7 @@
       <c r="AJ842" s="1"/>
       <c r="AK842" s="1"/>
     </row>
-    <row r="843" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:37" ht="15.95" customHeight="1">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -34172,7 +34178,7 @@
       <c r="AJ843" s="1"/>
       <c r="AK843" s="1"/>
     </row>
-    <row r="844" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:37" ht="15.95" customHeight="1">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -34211,7 +34217,7 @@
       <c r="AJ844" s="1"/>
       <c r="AK844" s="1"/>
     </row>
-    <row r="845" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:37" ht="15.95" customHeight="1">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -34250,7 +34256,7 @@
       <c r="AJ845" s="1"/>
       <c r="AK845" s="1"/>
     </row>
-    <row r="846" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:37" ht="15.95" customHeight="1">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -34289,7 +34295,7 @@
       <c r="AJ846" s="1"/>
       <c r="AK846" s="1"/>
     </row>
-    <row r="847" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:37" ht="15.95" customHeight="1">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -34328,7 +34334,7 @@
       <c r="AJ847" s="1"/>
       <c r="AK847" s="1"/>
     </row>
-    <row r="848" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:37" ht="15.95" customHeight="1">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -34367,7 +34373,7 @@
       <c r="AJ848" s="1"/>
       <c r="AK848" s="1"/>
     </row>
-    <row r="849" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:37" ht="15.95" customHeight="1">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -34406,7 +34412,7 @@
       <c r="AJ849" s="1"/>
       <c r="AK849" s="1"/>
     </row>
-    <row r="850" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:37" ht="15.95" customHeight="1">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -34445,7 +34451,7 @@
       <c r="AJ850" s="1"/>
       <c r="AK850" s="1"/>
     </row>
-    <row r="851" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:37" ht="15.95" customHeight="1">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -34484,7 +34490,7 @@
       <c r="AJ851" s="1"/>
       <c r="AK851" s="1"/>
     </row>
-    <row r="852" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:37" ht="15.95" customHeight="1">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -34523,7 +34529,7 @@
       <c r="AJ852" s="1"/>
       <c r="AK852" s="1"/>
     </row>
-    <row r="853" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:37" ht="15.95" customHeight="1">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -34562,7 +34568,7 @@
       <c r="AJ853" s="1"/>
       <c r="AK853" s="1"/>
     </row>
-    <row r="854" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:37" ht="15.95" customHeight="1">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -34601,7 +34607,7 @@
       <c r="AJ854" s="1"/>
       <c r="AK854" s="1"/>
     </row>
-    <row r="855" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:37" ht="15.95" customHeight="1">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -34640,7 +34646,7 @@
       <c r="AJ855" s="1"/>
       <c r="AK855" s="1"/>
     </row>
-    <row r="856" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:37" ht="15.95" customHeight="1">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -34679,7 +34685,7 @@
       <c r="AJ856" s="1"/>
       <c r="AK856" s="1"/>
     </row>
-    <row r="857" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:37" ht="15.95" customHeight="1">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -34718,7 +34724,7 @@
       <c r="AJ857" s="1"/>
       <c r="AK857" s="1"/>
     </row>
-    <row r="858" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:37" ht="15.95" customHeight="1">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -34757,7 +34763,7 @@
       <c r="AJ858" s="1"/>
       <c r="AK858" s="1"/>
     </row>
-    <row r="859" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:37" ht="15.95" customHeight="1">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -34796,7 +34802,7 @@
       <c r="AJ859" s="1"/>
       <c r="AK859" s="1"/>
     </row>
-    <row r="860" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:37" ht="15.95" customHeight="1">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -34835,7 +34841,7 @@
       <c r="AJ860" s="1"/>
       <c r="AK860" s="1"/>
     </row>
-    <row r="861" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="861" spans="1:37" ht="15.95" customHeight="1">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -34874,7 +34880,7 @@
       <c r="AJ861" s="1"/>
       <c r="AK861" s="1"/>
     </row>
-    <row r="862" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="862" spans="1:37" ht="15.95" customHeight="1">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -34913,7 +34919,7 @@
       <c r="AJ862" s="1"/>
       <c r="AK862" s="1"/>
     </row>
-    <row r="863" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="863" spans="1:37" ht="15.95" customHeight="1">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -34952,7 +34958,7 @@
       <c r="AJ863" s="1"/>
       <c r="AK863" s="1"/>
     </row>
-    <row r="864" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:37" ht="15.95" customHeight="1">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -34991,7 +34997,7 @@
       <c r="AJ864" s="1"/>
       <c r="AK864" s="1"/>
     </row>
-    <row r="865" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="865" spans="1:37" ht="15.95" customHeight="1">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -35030,7 +35036,7 @@
       <c r="AJ865" s="1"/>
       <c r="AK865" s="1"/>
     </row>
-    <row r="866" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="866" spans="1:37" ht="15.95" customHeight="1">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -35069,7 +35075,7 @@
       <c r="AJ866" s="1"/>
       <c r="AK866" s="1"/>
     </row>
-    <row r="867" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="867" spans="1:37" ht="15.95" customHeight="1">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -35108,7 +35114,7 @@
       <c r="AJ867" s="1"/>
       <c r="AK867" s="1"/>
     </row>
-    <row r="868" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="868" spans="1:37" ht="15.95" customHeight="1">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -35147,7 +35153,7 @@
       <c r="AJ868" s="1"/>
       <c r="AK868" s="1"/>
     </row>
-    <row r="869" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="869" spans="1:37" ht="15.95" customHeight="1">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -35186,7 +35192,7 @@
       <c r="AJ869" s="1"/>
       <c r="AK869" s="1"/>
     </row>
-    <row r="870" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="870" spans="1:37" ht="15.95" customHeight="1">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -35225,7 +35231,7 @@
       <c r="AJ870" s="1"/>
       <c r="AK870" s="1"/>
     </row>
-    <row r="871" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="871" spans="1:37" ht="15.95" customHeight="1">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -35264,7 +35270,7 @@
       <c r="AJ871" s="1"/>
       <c r="AK871" s="1"/>
     </row>
-    <row r="872" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="872" spans="1:37" ht="15.95" customHeight="1">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -35303,7 +35309,7 @@
       <c r="AJ872" s="1"/>
       <c r="AK872" s="1"/>
     </row>
-    <row r="873" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="873" spans="1:37" ht="15.95" customHeight="1">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -35342,7 +35348,7 @@
       <c r="AJ873" s="1"/>
       <c r="AK873" s="1"/>
     </row>
-    <row r="874" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="874" spans="1:37" ht="15.95" customHeight="1">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -35381,7 +35387,7 @@
       <c r="AJ874" s="1"/>
       <c r="AK874" s="1"/>
     </row>
-    <row r="875" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="875" spans="1:37" ht="15.95" customHeight="1">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -35420,7 +35426,7 @@
       <c r="AJ875" s="1"/>
       <c r="AK875" s="1"/>
     </row>
-    <row r="876" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="876" spans="1:37" ht="15.95" customHeight="1">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -35459,7 +35465,7 @@
       <c r="AJ876" s="1"/>
       <c r="AK876" s="1"/>
     </row>
-    <row r="877" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="877" spans="1:37" ht="15.95" customHeight="1">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -35498,7 +35504,7 @@
       <c r="AJ877" s="1"/>
       <c r="AK877" s="1"/>
     </row>
-    <row r="878" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="878" spans="1:37" ht="15.95" customHeight="1">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -35537,7 +35543,7 @@
       <c r="AJ878" s="1"/>
       <c r="AK878" s="1"/>
     </row>
-    <row r="879" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="879" spans="1:37" ht="15.95" customHeight="1">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -35576,7 +35582,7 @@
       <c r="AJ879" s="1"/>
       <c r="AK879" s="1"/>
     </row>
-    <row r="880" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="880" spans="1:37" ht="15.95" customHeight="1">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -35615,7 +35621,7 @@
       <c r="AJ880" s="1"/>
       <c r="AK880" s="1"/>
     </row>
-    <row r="881" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="881" spans="1:37" ht="15.95" customHeight="1">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -35654,7 +35660,7 @@
       <c r="AJ881" s="1"/>
       <c r="AK881" s="1"/>
     </row>
-    <row r="882" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="882" spans="1:37" ht="15.95" customHeight="1">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -35693,7 +35699,7 @@
       <c r="AJ882" s="1"/>
       <c r="AK882" s="1"/>
     </row>
-    <row r="883" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="883" spans="1:37" ht="15.95" customHeight="1">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -35732,7 +35738,7 @@
       <c r="AJ883" s="1"/>
       <c r="AK883" s="1"/>
     </row>
-    <row r="884" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="884" spans="1:37" ht="15.95" customHeight="1">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -35771,7 +35777,7 @@
       <c r="AJ884" s="1"/>
       <c r="AK884" s="1"/>
     </row>
-    <row r="885" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="885" spans="1:37" ht="15.95" customHeight="1">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -35810,7 +35816,7 @@
       <c r="AJ885" s="1"/>
       <c r="AK885" s="1"/>
     </row>
-    <row r="886" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:37" ht="15.95" customHeight="1">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -35849,7 +35855,7 @@
       <c r="AJ886" s="1"/>
       <c r="AK886" s="1"/>
     </row>
-    <row r="887" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:37" ht="15.95" customHeight="1">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -35888,7 +35894,7 @@
       <c r="AJ887" s="1"/>
       <c r="AK887" s="1"/>
     </row>
-    <row r="888" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:37" ht="15.95" customHeight="1">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -35927,7 +35933,7 @@
       <c r="AJ888" s="1"/>
       <c r="AK888" s="1"/>
     </row>
-    <row r="889" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:37" ht="15.95" customHeight="1">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -35966,7 +35972,7 @@
       <c r="AJ889" s="1"/>
       <c r="AK889" s="1"/>
     </row>
-    <row r="890" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:37" ht="15.95" customHeight="1">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -36005,7 +36011,7 @@
       <c r="AJ890" s="1"/>
       <c r="AK890" s="1"/>
     </row>
-    <row r="891" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:37" ht="15.95" customHeight="1">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -36044,7 +36050,7 @@
       <c r="AJ891" s="1"/>
       <c r="AK891" s="1"/>
     </row>
-    <row r="892" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:37" ht="15.95" customHeight="1">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -36083,7 +36089,7 @@
       <c r="AJ892" s="1"/>
       <c r="AK892" s="1"/>
     </row>
-    <row r="893" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:37" ht="15.95" customHeight="1">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -36122,7 +36128,7 @@
       <c r="AJ893" s="1"/>
       <c r="AK893" s="1"/>
     </row>
-    <row r="894" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:37" ht="15.95" customHeight="1">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -36161,7 +36167,7 @@
       <c r="AJ894" s="1"/>
       <c r="AK894" s="1"/>
     </row>
-    <row r="895" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:37" ht="15.95" customHeight="1">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -36200,7 +36206,7 @@
       <c r="AJ895" s="1"/>
       <c r="AK895" s="1"/>
     </row>
-    <row r="896" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:37" ht="15.95" customHeight="1">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -36239,7 +36245,7 @@
       <c r="AJ896" s="1"/>
       <c r="AK896" s="1"/>
     </row>
-    <row r="897" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:37" ht="15.95" customHeight="1">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -36278,7 +36284,7 @@
       <c r="AJ897" s="1"/>
       <c r="AK897" s="1"/>
     </row>
-    <row r="898" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:37" ht="15.95" customHeight="1">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -36317,7 +36323,7 @@
       <c r="AJ898" s="1"/>
       <c r="AK898" s="1"/>
     </row>
-    <row r="899" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:37" ht="15.95" customHeight="1">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -36356,7 +36362,7 @@
       <c r="AJ899" s="1"/>
       <c r="AK899" s="1"/>
     </row>
-    <row r="900" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:37" ht="15.95" customHeight="1">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -36395,7 +36401,7 @@
       <c r="AJ900" s="1"/>
       <c r="AK900" s="1"/>
     </row>
-    <row r="901" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:37" ht="15.95" customHeight="1">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -36434,7 +36440,7 @@
       <c r="AJ901" s="1"/>
       <c r="AK901" s="1"/>
     </row>
-    <row r="902" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:37" ht="15.95" customHeight="1">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -36473,7 +36479,7 @@
       <c r="AJ902" s="1"/>
       <c r="AK902" s="1"/>
     </row>
-    <row r="903" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:37" ht="15.95" customHeight="1">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -36512,7 +36518,7 @@
       <c r="AJ903" s="1"/>
       <c r="AK903" s="1"/>
     </row>
-    <row r="904" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:37" ht="15.95" customHeight="1">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -36551,7 +36557,7 @@
       <c r="AJ904" s="1"/>
       <c r="AK904" s="1"/>
     </row>
-    <row r="905" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:37" ht="15.95" customHeight="1">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -36590,7 +36596,7 @@
       <c r="AJ905" s="1"/>
       <c r="AK905" s="1"/>
     </row>
-    <row r="906" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:37" ht="15.95" customHeight="1">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -36629,7 +36635,7 @@
       <c r="AJ906" s="1"/>
       <c r="AK906" s="1"/>
     </row>
-    <row r="907" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="907" spans="1:37" ht="15.95" customHeight="1">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -36668,7 +36674,7 @@
       <c r="AJ907" s="1"/>
       <c r="AK907" s="1"/>
     </row>
-    <row r="908" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="908" spans="1:37" ht="15.95" customHeight="1">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -36707,7 +36713,7 @@
       <c r="AJ908" s="1"/>
       <c r="AK908" s="1"/>
     </row>
-    <row r="909" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="909" spans="1:37" ht="15.95" customHeight="1">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -36746,7 +36752,7 @@
       <c r="AJ909" s="1"/>
       <c r="AK909" s="1"/>
     </row>
-    <row r="910" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="910" spans="1:37" ht="15.95" customHeight="1">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -36785,7 +36791,7 @@
       <c r="AJ910" s="1"/>
       <c r="AK910" s="1"/>
     </row>
-    <row r="911" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="911" spans="1:37" ht="15.95" customHeight="1">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -36824,7 +36830,7 @@
       <c r="AJ911" s="1"/>
       <c r="AK911" s="1"/>
     </row>
-    <row r="912" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="912" spans="1:37" ht="15.95" customHeight="1">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -36863,7 +36869,7 @@
       <c r="AJ912" s="1"/>
       <c r="AK912" s="1"/>
     </row>
-    <row r="913" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="913" spans="1:37" ht="15.95" customHeight="1">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -36902,7 +36908,7 @@
       <c r="AJ913" s="1"/>
       <c r="AK913" s="1"/>
     </row>
-    <row r="914" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="914" spans="1:37" ht="15.95" customHeight="1">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -36941,7 +36947,7 @@
       <c r="AJ914" s="1"/>
       <c r="AK914" s="1"/>
     </row>
-    <row r="915" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="915" spans="1:37" ht="15.95" customHeight="1">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -36980,7 +36986,7 @@
       <c r="AJ915" s="1"/>
       <c r="AK915" s="1"/>
     </row>
-    <row r="916" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="916" spans="1:37" ht="15.95" customHeight="1">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -37019,7 +37025,7 @@
       <c r="AJ916" s="1"/>
       <c r="AK916" s="1"/>
     </row>
-    <row r="917" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="917" spans="1:37" ht="15.95" customHeight="1">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -37058,7 +37064,7 @@
       <c r="AJ917" s="1"/>
       <c r="AK917" s="1"/>
     </row>
-    <row r="918" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="918" spans="1:37" ht="15.95" customHeight="1">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -37097,7 +37103,7 @@
       <c r="AJ918" s="1"/>
       <c r="AK918" s="1"/>
     </row>
-    <row r="919" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="919" spans="1:37" ht="15.95" customHeight="1">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -37136,7 +37142,7 @@
       <c r="AJ919" s="1"/>
       <c r="AK919" s="1"/>
     </row>
-    <row r="920" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="920" spans="1:37" ht="15.95" customHeight="1">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -37175,7 +37181,7 @@
       <c r="AJ920" s="1"/>
       <c r="AK920" s="1"/>
     </row>
-    <row r="921" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="921" spans="1:37" ht="15.95" customHeight="1">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -37214,7 +37220,7 @@
       <c r="AJ921" s="1"/>
       <c r="AK921" s="1"/>
     </row>
-    <row r="922" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="922" spans="1:37" ht="15.95" customHeight="1">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -37253,7 +37259,7 @@
       <c r="AJ922" s="1"/>
       <c r="AK922" s="1"/>
     </row>
-    <row r="923" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="923" spans="1:37" ht="15.95" customHeight="1">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -37292,7 +37298,7 @@
       <c r="AJ923" s="1"/>
       <c r="AK923" s="1"/>
     </row>
-    <row r="924" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="924" spans="1:37" ht="15.95" customHeight="1">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -37331,7 +37337,7 @@
       <c r="AJ924" s="1"/>
       <c r="AK924" s="1"/>
     </row>
-    <row r="925" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="925" spans="1:37" ht="15.95" customHeight="1">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -37370,7 +37376,7 @@
       <c r="AJ925" s="1"/>
       <c r="AK925" s="1"/>
     </row>
-    <row r="926" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="926" spans="1:37" ht="15.95" customHeight="1">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -37409,7 +37415,7 @@
       <c r="AJ926" s="1"/>
       <c r="AK926" s="1"/>
     </row>
-    <row r="927" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="927" spans="1:37" ht="15.95" customHeight="1">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -37448,7 +37454,7 @@
       <c r="AJ927" s="1"/>
       <c r="AK927" s="1"/>
     </row>
-    <row r="928" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="928" spans="1:37" ht="15.95" customHeight="1">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -37487,7 +37493,7 @@
       <c r="AJ928" s="1"/>
       <c r="AK928" s="1"/>
     </row>
-    <row r="929" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="929" spans="1:37" ht="15.95" customHeight="1">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -37526,7 +37532,7 @@
       <c r="AJ929" s="1"/>
       <c r="AK929" s="1"/>
     </row>
-    <row r="930" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="930" spans="1:37" ht="15.95" customHeight="1">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -37565,7 +37571,7 @@
       <c r="AJ930" s="1"/>
       <c r="AK930" s="1"/>
     </row>
-    <row r="931" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="931" spans="1:37" ht="15.95" customHeight="1">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -37604,7 +37610,7 @@
       <c r="AJ931" s="1"/>
       <c r="AK931" s="1"/>
     </row>
-    <row r="932" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="932" spans="1:37" ht="15.95" customHeight="1">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -37643,7 +37649,7 @@
       <c r="AJ932" s="1"/>
       <c r="AK932" s="1"/>
     </row>
-    <row r="933" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="933" spans="1:37" ht="15.95" customHeight="1">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -37682,7 +37688,7 @@
       <c r="AJ933" s="1"/>
       <c r="AK933" s="1"/>
     </row>
-    <row r="934" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="934" spans="1:37" ht="15.95" customHeight="1">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -37721,7 +37727,7 @@
       <c r="AJ934" s="1"/>
       <c r="AK934" s="1"/>
     </row>
-    <row r="935" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="935" spans="1:37" ht="15.95" customHeight="1">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -37760,7 +37766,7 @@
       <c r="AJ935" s="1"/>
       <c r="AK935" s="1"/>
     </row>
-    <row r="936" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="936" spans="1:37" ht="15.95" customHeight="1">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -37799,7 +37805,7 @@
       <c r="AJ936" s="1"/>
       <c r="AK936" s="1"/>
     </row>
-    <row r="937" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="937" spans="1:37" ht="15.95" customHeight="1">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -37838,7 +37844,7 @@
       <c r="AJ937" s="1"/>
       <c r="AK937" s="1"/>
     </row>
-    <row r="938" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="938" spans="1:37" ht="15.95" customHeight="1">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -37877,7 +37883,7 @@
       <c r="AJ938" s="1"/>
       <c r="AK938" s="1"/>
     </row>
-    <row r="939" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="939" spans="1:37" ht="15.95" customHeight="1">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -37916,7 +37922,7 @@
       <c r="AJ939" s="1"/>
       <c r="AK939" s="1"/>
     </row>
-    <row r="940" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="940" spans="1:37" ht="15.95" customHeight="1">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -37955,7 +37961,7 @@
       <c r="AJ940" s="1"/>
       <c r="AK940" s="1"/>
     </row>
-    <row r="941" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="941" spans="1:37" ht="15.95" customHeight="1">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -37994,7 +38000,7 @@
       <c r="AJ941" s="1"/>
       <c r="AK941" s="1"/>
     </row>
-    <row r="942" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="942" spans="1:37" ht="15.95" customHeight="1">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -38033,7 +38039,7 @@
       <c r="AJ942" s="1"/>
       <c r="AK942" s="1"/>
     </row>
-    <row r="943" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="943" spans="1:37" ht="15.95" customHeight="1">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -38072,7 +38078,7 @@
       <c r="AJ943" s="1"/>
       <c r="AK943" s="1"/>
     </row>
-    <row r="944" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="944" spans="1:37" ht="15.95" customHeight="1">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -38111,7 +38117,7 @@
       <c r="AJ944" s="1"/>
       <c r="AK944" s="1"/>
     </row>
-    <row r="945" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="945" spans="1:37" ht="15.95" customHeight="1">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -38150,7 +38156,7 @@
       <c r="AJ945" s="1"/>
       <c r="AK945" s="1"/>
     </row>
-    <row r="946" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="946" spans="1:37" ht="15.95" customHeight="1">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -38189,7 +38195,7 @@
       <c r="AJ946" s="1"/>
       <c r="AK946" s="1"/>
     </row>
-    <row r="947" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="947" spans="1:37" ht="15.95" customHeight="1">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -38228,7 +38234,7 @@
       <c r="AJ947" s="1"/>
       <c r="AK947" s="1"/>
     </row>
-    <row r="948" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="948" spans="1:37" ht="15.95" customHeight="1">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -38267,7 +38273,7 @@
       <c r="AJ948" s="1"/>
       <c r="AK948" s="1"/>
     </row>
-    <row r="949" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="949" spans="1:37" ht="15.95" customHeight="1">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -38306,7 +38312,7 @@
       <c r="AJ949" s="1"/>
       <c r="AK949" s="1"/>
     </row>
-    <row r="950" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="950" spans="1:37" ht="15.95" customHeight="1">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -38345,7 +38351,7 @@
       <c r="AJ950" s="1"/>
       <c r="AK950" s="1"/>
     </row>
-    <row r="951" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="951" spans="1:37" ht="15.95" customHeight="1">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -38384,7 +38390,7 @@
       <c r="AJ951" s="1"/>
       <c r="AK951" s="1"/>
     </row>
-    <row r="952" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="952" spans="1:37" ht="15.95" customHeight="1">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -38423,7 +38429,7 @@
       <c r="AJ952" s="1"/>
       <c r="AK952" s="1"/>
     </row>
-    <row r="953" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="953" spans="1:37" ht="15.95" customHeight="1">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -38462,7 +38468,7 @@
       <c r="AJ953" s="1"/>
       <c r="AK953" s="1"/>
     </row>
-    <row r="954" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="954" spans="1:37" ht="15.95" customHeight="1">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -38501,7 +38507,7 @@
       <c r="AJ954" s="1"/>
       <c r="AK954" s="1"/>
     </row>
-    <row r="955" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="955" spans="1:37" ht="15.95" customHeight="1">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -38540,7 +38546,7 @@
       <c r="AJ955" s="1"/>
       <c r="AK955" s="1"/>
     </row>
-    <row r="956" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="956" spans="1:37" ht="15.95" customHeight="1">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -38579,7 +38585,7 @@
       <c r="AJ956" s="1"/>
       <c r="AK956" s="1"/>
     </row>
-    <row r="957" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="957" spans="1:37" ht="15.95" customHeight="1">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -38618,7 +38624,7 @@
       <c r="AJ957" s="1"/>
       <c r="AK957" s="1"/>
     </row>
-    <row r="958" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="958" spans="1:37" ht="15.95" customHeight="1">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -38657,7 +38663,7 @@
       <c r="AJ958" s="1"/>
       <c r="AK958" s="1"/>
     </row>
-    <row r="959" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="959" spans="1:37" ht="15.95" customHeight="1">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -38696,7 +38702,7 @@
       <c r="AJ959" s="1"/>
       <c r="AK959" s="1"/>
     </row>
-    <row r="960" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="960" spans="1:37" ht="15.95" customHeight="1">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -38735,7 +38741,7 @@
       <c r="AJ960" s="1"/>
       <c r="AK960" s="1"/>
     </row>
-    <row r="961" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="961" spans="1:37" ht="15.95" customHeight="1">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -38774,7 +38780,7 @@
       <c r="AJ961" s="1"/>
       <c r="AK961" s="1"/>
     </row>
-    <row r="962" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="962" spans="1:37" ht="15.95" customHeight="1">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -38813,7 +38819,7 @@
       <c r="AJ962" s="1"/>
       <c r="AK962" s="1"/>
     </row>
-    <row r="963" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="963" spans="1:37" ht="15.95" customHeight="1">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -38852,7 +38858,7 @@
       <c r="AJ963" s="1"/>
       <c r="AK963" s="1"/>
     </row>
-    <row r="964" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="964" spans="1:37" ht="15.95" customHeight="1">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -38891,7 +38897,7 @@
       <c r="AJ964" s="1"/>
       <c r="AK964" s="1"/>
     </row>
-    <row r="965" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="965" spans="1:37" ht="15.95" customHeight="1">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -38930,7 +38936,7 @@
       <c r="AJ965" s="1"/>
       <c r="AK965" s="1"/>
     </row>
-    <row r="966" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="966" spans="1:37" ht="15.95" customHeight="1">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -38969,7 +38975,7 @@
       <c r="AJ966" s="1"/>
       <c r="AK966" s="1"/>
     </row>
-    <row r="967" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="967" spans="1:37" ht="15.95" customHeight="1">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -39008,7 +39014,7 @@
       <c r="AJ967" s="1"/>
       <c r="AK967" s="1"/>
     </row>
-    <row r="968" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="968" spans="1:37" ht="15.95" customHeight="1">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -39047,7 +39053,7 @@
       <c r="AJ968" s="1"/>
       <c r="AK968" s="1"/>
     </row>
-    <row r="969" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="969" spans="1:37" ht="15.95" customHeight="1">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -39086,7 +39092,7 @@
       <c r="AJ969" s="1"/>
       <c r="AK969" s="1"/>
     </row>
-    <row r="970" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="970" spans="1:37" ht="15.95" customHeight="1">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -39125,7 +39131,7 @@
       <c r="AJ970" s="1"/>
       <c r="AK970" s="1"/>
     </row>
-    <row r="971" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="971" spans="1:37" ht="15.95" customHeight="1">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -39164,7 +39170,7 @@
       <c r="AJ971" s="1"/>
       <c r="AK971" s="1"/>
     </row>
-    <row r="972" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="972" spans="1:37" ht="15.95" customHeight="1">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -39203,7 +39209,7 @@
       <c r="AJ972" s="1"/>
       <c r="AK972" s="1"/>
     </row>
-    <row r="973" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="973" spans="1:37" ht="15.95" customHeight="1">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -39242,7 +39248,7 @@
       <c r="AJ973" s="1"/>
       <c r="AK973" s="1"/>
     </row>
-    <row r="974" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="974" spans="1:37" ht="15.95" customHeight="1">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -39281,7 +39287,7 @@
       <c r="AJ974" s="1"/>
       <c r="AK974" s="1"/>
     </row>
-    <row r="975" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="975" spans="1:37" ht="15.95" customHeight="1">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -39320,7 +39326,7 @@
       <c r="AJ975" s="1"/>
       <c r="AK975" s="1"/>
     </row>
-    <row r="976" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="976" spans="1:37" ht="15.95" customHeight="1">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -39359,7 +39365,7 @@
       <c r="AJ976" s="1"/>
       <c r="AK976" s="1"/>
     </row>
-    <row r="977" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="977" spans="1:37" ht="15.95" customHeight="1">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -39398,7 +39404,7 @@
       <c r="AJ977" s="1"/>
       <c r="AK977" s="1"/>
     </row>
-    <row r="978" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="978" spans="1:37" ht="15.95" customHeight="1">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -39437,7 +39443,7 @@
       <c r="AJ978" s="1"/>
       <c r="AK978" s="1"/>
     </row>
-    <row r="979" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="979" spans="1:37" ht="15.95" customHeight="1">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -39476,7 +39482,7 @@
       <c r="AJ979" s="1"/>
       <c r="AK979" s="1"/>
     </row>
-    <row r="980" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="980" spans="1:37" ht="15.95" customHeight="1">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -39515,7 +39521,7 @@
       <c r="AJ980" s="1"/>
       <c r="AK980" s="1"/>
     </row>
-    <row r="981" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="981" spans="1:37" ht="15.95" customHeight="1">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -39554,7 +39560,7 @@
       <c r="AJ981" s="1"/>
       <c r="AK981" s="1"/>
     </row>
-    <row r="982" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="982" spans="1:37" ht="15.95" customHeight="1">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -39593,7 +39599,7 @@
       <c r="AJ982" s="1"/>
       <c r="AK982" s="1"/>
     </row>
-    <row r="983" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="983" spans="1:37" ht="15.95" customHeight="1">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -39632,7 +39638,7 @@
       <c r="AJ983" s="1"/>
       <c r="AK983" s="1"/>
     </row>
-    <row r="984" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="984" spans="1:37" ht="15.95" customHeight="1">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -39671,7 +39677,7 @@
       <c r="AJ984" s="1"/>
       <c r="AK984" s="1"/>
     </row>
-    <row r="985" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="985" spans="1:37" ht="15.95" customHeight="1">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -39710,7 +39716,7 @@
       <c r="AJ985" s="1"/>
       <c r="AK985" s="1"/>
     </row>
-    <row r="986" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="986" spans="1:37" ht="15.95" customHeight="1">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -39749,7 +39755,7 @@
       <c r="AJ986" s="1"/>
       <c r="AK986" s="1"/>
     </row>
-    <row r="987" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="987" spans="1:37" ht="15.95" customHeight="1">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -39788,7 +39794,7 @@
       <c r="AJ987" s="1"/>
       <c r="AK987" s="1"/>
     </row>
-    <row r="988" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="988" spans="1:37" ht="15.95" customHeight="1">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -39827,7 +39833,7 @@
       <c r="AJ988" s="1"/>
       <c r="AK988" s="1"/>
     </row>
-    <row r="989" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="989" spans="1:37" ht="15.95" customHeight="1">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -39866,7 +39872,7 @@
       <c r="AJ989" s="1"/>
       <c r="AK989" s="1"/>
     </row>
-    <row r="990" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="990" spans="1:37" ht="15.95" customHeight="1">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -39905,7 +39911,7 @@
       <c r="AJ990" s="1"/>
       <c r="AK990" s="1"/>
     </row>
-    <row r="991" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="991" spans="1:37" ht="15.95" customHeight="1">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -39944,7 +39950,7 @@
       <c r="AJ991" s="1"/>
       <c r="AK991" s="1"/>
     </row>
-    <row r="992" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="992" spans="1:37" ht="15.95" customHeight="1">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -39983,7 +39989,7 @@
       <c r="AJ992" s="1"/>
       <c r="AK992" s="1"/>
     </row>
-    <row r="993" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="993" spans="1:37" ht="15.95" customHeight="1">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -40022,7 +40028,7 @@
       <c r="AJ993" s="1"/>
       <c r="AK993" s="1"/>
     </row>
-    <row r="994" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="994" spans="1:37" ht="15.95" customHeight="1">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -40061,7 +40067,7 @@
       <c r="AJ994" s="1"/>
       <c r="AK994" s="1"/>
     </row>
-    <row r="995" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="995" spans="1:37" ht="15.95" customHeight="1">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -40100,7 +40106,7 @@
       <c r="AJ995" s="1"/>
       <c r="AK995" s="1"/>
     </row>
-    <row r="996" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="996" spans="1:37" ht="15.95" customHeight="1">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -40139,7 +40145,7 @@
       <c r="AJ996" s="1"/>
       <c r="AK996" s="1"/>
     </row>
-    <row r="997" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="997" spans="1:37" ht="15.95" customHeight="1">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -40178,7 +40184,7 @@
       <c r="AJ997" s="1"/>
       <c r="AK997" s="1"/>
     </row>
-    <row r="998" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="998" spans="1:37" ht="15.95" customHeight="1">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -40217,7 +40223,7 @@
       <c r="AJ998" s="1"/>
       <c r="AK998" s="1"/>
     </row>
-    <row r="999" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="999" spans="1:37" ht="15.95" customHeight="1">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -40256,7 +40262,7 @@
       <c r="AJ999" s="1"/>
       <c r="AK999" s="1"/>
     </row>
-    <row r="1000" spans="1:37" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1000" spans="1:37" ht="15.95" customHeight="1">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -40303,6 +40309,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="06a0b0f5-ab3f-4382-8730-459fb424e421" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="26f1519c-0a18-4175-bd8e-760b6597752e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100473DE4EA8FF5104F8456752DB619673A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e4fd7ef94a58df89505d05cd8f0789b1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="26f1519c-0a18-4175-bd8e-760b6597752e" xmlns:ns3="def454d3-7361-4a53-bd39-35a8c96a39c0" xmlns:ns4="06a0b0f5-ab3f-4382-8730-459fb424e421" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="14f03c0bfa8338aae8ff84ba27968e08" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -40559,19 +40578,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="06a0b0f5-ab3f-4382-8730-459fb424e421" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="26f1519c-0a18-4175-bd8e-760b6597752e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -40582,44 +40588,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EADD83C0-97A3-4575-BA2B-2B923FC5B67B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="26f1519c-0a18-4175-bd8e-760b6597752e"/>
-    <ds:schemaRef ds:uri="def454d3-7361-4a53-bd39-35a8c96a39c0"/>
-    <ds:schemaRef ds:uri="06a0b0f5-ab3f-4382-8730-459fb424e421"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44B7B1D8-F3F2-46A8-A792-B679C78EEEEB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44B7B1D8-F3F2-46A8-A792-B679C78EEEEB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="06a0b0f5-ab3f-4382-8730-459fb424e421"/>
-    <ds:schemaRef ds:uri="26f1519c-0a18-4175-bd8e-760b6597752e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EADD83C0-97A3-4575-BA2B-2B923FC5B67B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D55B629F-9BAD-43E6-819F-B097A47F8C05}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D55B629F-9BAD-43E6-819F-B097A47F8C05}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
